--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126380575</v>
+        <v>126380581</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Provåker, Ång</t>
+          <t>Öreström, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691837</v>
+        <v>691971</v>
       </c>
       <c r="R3" t="n">
-        <v>7106446</v>
+        <v>7106784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,17 +856,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126380581</v>
+        <v>126380575</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öreström, Ång</t>
+          <t>Provåker, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691971</v>
+        <v>691837</v>
       </c>
       <c r="R4" t="n">
-        <v>7106784</v>
+        <v>7106446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,17 +968,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126380578</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126380581</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126380575</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>126380579</v>
       </c>
       <c r="B5" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126380581</v>
+        <v>126380575</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öreström, Ång</t>
+          <t>Provåker, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691971</v>
+        <v>691837</v>
       </c>
       <c r="R3" t="n">
-        <v>7106784</v>
+        <v>7106446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,17 +856,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126380575</v>
+        <v>126380581</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Provåker, Ång</t>
+          <t>Öreström, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691837</v>
+        <v>691971</v>
       </c>
       <c r="R4" t="n">
-        <v>7106446</v>
+        <v>7106784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,17 +968,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -996,45 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126862876</v>
+        <v>126867049</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>92615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691847</v>
+        <v>691961</v>
       </c>
       <c r="R5" t="n">
-        <v>7106392</v>
+        <v>7106020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,18 +1078,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1097,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126862884</v>
+        <v>126862876</v>
       </c>
       <c r="B6" t="n">
         <v>98442</v>
@@ -1132,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691817</v>
+        <v>691847</v>
       </c>
       <c r="R6" t="n">
-        <v>7106456</v>
+        <v>7106392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,32 +1202,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868503</v>
+        <v>126862884</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692149</v>
+        <v>691817</v>
       </c>
       <c r="R7" t="n">
-        <v>7106588</v>
+        <v>7106456</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,12 +1287,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1299,7 +1303,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126868496</v>
+        <v>126868503</v>
       </c>
       <c r="B8" t="n">
         <v>79014</v>
@@ -1334,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691941</v>
+        <v>692149</v>
       </c>
       <c r="R8" t="n">
-        <v>7106860</v>
+        <v>7106588</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,48 +1404,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867049</v>
+        <v>126868496</v>
       </c>
       <c r="B9" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691961</v>
+        <v>691941</v>
       </c>
       <c r="R9" t="n">
-        <v>7106020</v>
+        <v>7106860</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,19 +1483,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -5688,32 +5688,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126867680</v>
+        <v>126867609</v>
       </c>
       <c r="B51" t="n">
-        <v>92615</v>
+        <v>78772</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691998</v>
+        <v>691764</v>
       </c>
       <c r="R51" t="n">
-        <v>7106190</v>
+        <v>7106568</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5789,32 +5789,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126867609</v>
+        <v>126867680</v>
       </c>
       <c r="B52" t="n">
-        <v>78772</v>
+        <v>92615</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691764</v>
+        <v>691998</v>
       </c>
       <c r="R52" t="n">
-        <v>7106568</v>
+        <v>7106190</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126867613</v>
+        <v>126868507</v>
       </c>
       <c r="B75" t="n">
         <v>79014</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>691720</v>
+        <v>691973</v>
       </c>
       <c r="R75" t="n">
-        <v>7106626</v>
+        <v>7106021</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8229,12 +8229,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126867636</v>
+        <v>126867613</v>
       </c>
       <c r="B76" t="n">
         <v>79014</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>691954</v>
+        <v>691720</v>
       </c>
       <c r="R76" t="n">
-        <v>7106198</v>
+        <v>7106626</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8346,7 +8346,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126867625</v>
+        <v>126867636</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>691792</v>
+        <v>691954</v>
       </c>
       <c r="R77" t="n">
-        <v>7106323</v>
+        <v>7106198</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126865527</v>
+        <v>126867625</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8458,21 +8458,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>691852</v>
+        <v>691792</v>
       </c>
       <c r="R78" t="n">
-        <v>7106251</v>
+        <v>7106323</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8532,12 +8532,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8548,7 +8548,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126868317</v>
+        <v>126865527</v>
       </c>
       <c r="B79" t="n">
         <v>80117</v>
@@ -8583,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>691833</v>
+        <v>691852</v>
       </c>
       <c r="R79" t="n">
-        <v>7106362</v>
+        <v>7106251</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8621,11 +8621,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På  "sälg låga".</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8638,12 +8633,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8654,10 +8649,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126868507</v>
+        <v>126868317</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,21 +8660,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8689,10 +8684,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>691973</v>
+        <v>691833</v>
       </c>
       <c r="R80" t="n">
-        <v>7106021</v>
+        <v>7106362</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8727,6 +8722,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På  "sälg låga".</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8739,12 +8739,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8957,7 +8957,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126867627</v>
+        <v>126868492</v>
       </c>
       <c r="B83" t="n">
         <v>79014</v>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>691826</v>
+        <v>692005</v>
       </c>
       <c r="R83" t="n">
-        <v>7106291</v>
+        <v>7106694</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9042,12 +9042,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9058,45 +9058,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126868492</v>
+        <v>126862859</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>692005</v>
+        <v>691967</v>
       </c>
       <c r="R84" t="n">
-        <v>7106694</v>
+        <v>7106021</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9131,6 +9139,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Solgrop och tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9143,12 +9156,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9159,53 +9172,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126862859</v>
+        <v>126865530</v>
       </c>
       <c r="B85" t="n">
-        <v>56849</v>
+        <v>98442</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>691967</v>
+        <v>691847</v>
       </c>
       <c r="R85" t="n">
-        <v>7106021</v>
+        <v>7106512</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9240,11 +9245,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Solgrop och tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9257,12 +9257,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9273,32 +9273,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126865530</v>
+        <v>126867627</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>691847</v>
+        <v>691826</v>
       </c>
       <c r="R86" t="n">
-        <v>7106512</v>
+        <v>7106291</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9358,12 +9358,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -12732,10 +12732,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126868494</v>
+        <v>126868318</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12743,21 +12743,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>691985</v>
+        <v>691844</v>
       </c>
       <c r="R120" t="n">
-        <v>7106752</v>
+        <v>7106329</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12805,6 +12805,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12817,12 +12822,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12833,45 +12838,49 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126868497</v>
+        <v>126862191</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>691928</v>
+        <v>691819</v>
       </c>
       <c r="R121" t="n">
-        <v>7106864</v>
+        <v>7106338</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12906,29 +12915,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På gammal grov gran</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12939,32 +12944,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126868464</v>
+        <v>126868326</v>
       </c>
       <c r="B122" t="n">
-        <v>75138</v>
+        <v>98442</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12974,10 +12979,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>692154</v>
+        <v>691820</v>
       </c>
       <c r="R122" t="n">
-        <v>7106591</v>
+        <v>7106411</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13012,6 +13017,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13024,12 +13034,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13040,32 +13050,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126867594</v>
+        <v>126868494</v>
       </c>
       <c r="B123" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13075,10 +13085,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>691827</v>
+        <v>691985</v>
       </c>
       <c r="R123" t="n">
-        <v>7106280</v>
+        <v>7106752</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13125,12 +13135,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13141,32 +13151,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126868473</v>
+        <v>126868497</v>
       </c>
       <c r="B124" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13176,10 +13186,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691977</v>
+        <v>691928</v>
       </c>
       <c r="R124" t="n">
-        <v>7106779</v>
+        <v>7106864</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13214,13 +13224,17 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På gammal grov gran</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13232,7 +13246,7 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13243,10 +13257,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126868318</v>
+        <v>126868464</v>
       </c>
       <c r="B125" t="n">
-        <v>80117</v>
+        <v>75138</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13254,21 +13268,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13278,10 +13292,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>691844</v>
+        <v>692154</v>
       </c>
       <c r="R125" t="n">
-        <v>7106329</v>
+        <v>7106591</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13316,11 +13330,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -13333,12 +13342,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13349,32 +13358,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126862886</v>
+        <v>126867594</v>
       </c>
       <c r="B126" t="n">
-        <v>98442</v>
+        <v>79038</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13384,10 +13393,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>691817</v>
+        <v>691827</v>
       </c>
       <c r="R126" t="n">
-        <v>7106463</v>
+        <v>7106280</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13434,12 +13443,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13450,49 +13459,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126862191</v>
+        <v>126868473</v>
       </c>
       <c r="B127" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691819</v>
+        <v>691977</v>
       </c>
       <c r="R127" t="n">
-        <v>7106338</v>
+        <v>7106779</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13540,12 +13545,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13556,7 +13561,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126868326</v>
+        <v>126862886</v>
       </c>
       <c r="B128" t="n">
         <v>98442</v>
@@ -13591,10 +13596,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>691820</v>
+        <v>691817</v>
       </c>
       <c r="R128" t="n">
-        <v>7106411</v>
+        <v>7106463</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13629,11 +13634,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13646,12 +13646,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -16412,10 +16412,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126868306</v>
+        <v>126869140</v>
       </c>
       <c r="B156" t="n">
-        <v>56849</v>
+        <v>92615</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16423,37 +16423,37 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691780</v>
+        <v>691890</v>
       </c>
       <c r="R156" t="n">
-        <v>7105851</v>
+        <v>7105836</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16483,11 +16483,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Spår balning.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16502,12 +16497,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16518,10 +16513,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126869140</v>
+        <v>126868306</v>
       </c>
       <c r="B157" t="n">
-        <v>92615</v>
+        <v>56849</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16529,37 +16524,37 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691890</v>
+        <v>691780</v>
       </c>
       <c r="R157" t="n">
-        <v>7105836</v>
+        <v>7105851</v>
       </c>
       <c r="S157" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16589,6 +16584,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Spår balning.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16603,12 +16603,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -17137,32 +17137,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126851600</v>
+        <v>126867676</v>
       </c>
       <c r="B163" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17172,10 +17172,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691807</v>
+        <v>691698</v>
       </c>
       <c r="R163" t="n">
-        <v>7105857</v>
+        <v>7105935</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17222,44 +17222,48 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126867676</v>
+        <v>126851600</v>
       </c>
       <c r="B164" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17269,10 +17273,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>691698</v>
+        <v>691807</v>
       </c>
       <c r="R164" t="n">
-        <v>7105935</v>
+        <v>7105857</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17319,19 +17323,15 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17545,45 +17545,57 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126868470</v>
+        <v>126862862</v>
       </c>
       <c r="B167" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691906</v>
+        <v>691772</v>
       </c>
       <c r="R167" t="n">
-        <v>7105789</v>
+        <v>7105816</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17618,6 +17630,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Flygfärdig kyckling med höna</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -17630,12 +17647,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17646,32 +17663,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126862170</v>
+        <v>126862465</v>
       </c>
       <c r="B168" t="n">
-        <v>79632</v>
+        <v>98463</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17681,10 +17698,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691866</v>
+        <v>691913</v>
       </c>
       <c r="R168" t="n">
-        <v>7105795</v>
+        <v>7105810</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17719,6 +17736,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>&gt;10 ex</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17731,73 +17753,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126862862</v>
+        <v>126868470</v>
       </c>
       <c r="B169" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691772</v>
+        <v>691906</v>
       </c>
       <c r="R169" t="n">
-        <v>7105816</v>
+        <v>7105789</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17832,11 +17838,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Flygfärdig kyckling med höna</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17849,12 +17850,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17865,32 +17866,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126862465</v>
+        <v>126862170</v>
       </c>
       <c r="B170" t="n">
-        <v>98463</v>
+        <v>79632</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17900,10 +17901,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691913</v>
+        <v>691866</v>
       </c>
       <c r="R170" t="n">
-        <v>7105810</v>
+        <v>7105795</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17938,11 +17939,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>&gt;10 ex</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -17955,15 +17951,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20407,10 +20407,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126855647</v>
+        <v>126868499</v>
       </c>
       <c r="B195" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20418,21 +20418,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20442,10 +20442,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>692383</v>
+        <v>691849</v>
       </c>
       <c r="R195" t="n">
-        <v>7106365</v>
+        <v>7106968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20480,6 +20480,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -20492,61 +20497,61 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY195" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126868471</v>
+        <v>126855647</v>
       </c>
       <c r="B196" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>692149</v>
+        <v>692383</v>
       </c>
       <c r="R196" t="n">
-        <v>7106995</v>
+        <v>7106365</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20581,11 +20586,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
@@ -20598,61 +20598,61 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126868499</v>
+        <v>126868471</v>
       </c>
       <c r="B197" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691849</v>
+        <v>692149</v>
       </c>
       <c r="R197" t="n">
-        <v>7106968</v>
+        <v>7106995</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20689,7 +20689,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20709,7 +20709,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Maria  Persbo , Peter Andersson, Emil Lindgren, Lisa Requin, Miriam Schenk, Lise Mortensen, Elin Kannerby, Isac Enetjärn, Lars-Erik Nilsson, Nicklas Gustavsson, Beke Regelin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -22748,10 +22748,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126863144</v>
+        <v>126862179</v>
       </c>
       <c r="B218" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22759,21 +22759,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22783,10 +22783,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>692913</v>
+        <v>692087</v>
       </c>
       <c r="R218" t="n">
-        <v>7105995</v>
+        <v>7107184</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22833,12 +22833,12 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
@@ -22849,7 +22849,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126862179</v>
+        <v>126863148</v>
       </c>
       <c r="B219" t="n">
         <v>78773</v>
@@ -22884,10 +22884,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>692087</v>
+        <v>693009</v>
       </c>
       <c r="R219" t="n">
-        <v>7107184</v>
+        <v>7105804</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22934,12 +22934,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -22950,10 +22950,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>126863148</v>
+        <v>126863144</v>
       </c>
       <c r="B220" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22961,21 +22961,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22985,10 +22985,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693009</v>
+        <v>692913</v>
       </c>
       <c r="R220" t="n">
-        <v>7105804</v>
+        <v>7105995</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -996,48 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126867049</v>
+        <v>126868503</v>
       </c>
       <c r="B5" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691961</v>
+        <v>692149</v>
       </c>
       <c r="R5" t="n">
-        <v>7106020</v>
+        <v>7106588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1075,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1101,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126867602</v>
+        <v>126868496</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1108,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691670</v>
+        <v>691941</v>
       </c>
       <c r="R6" t="n">
-        <v>7106776</v>
+        <v>7106860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1202,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868503</v>
+        <v>126865523</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692149</v>
+        <v>691797</v>
       </c>
       <c r="R7" t="n">
-        <v>7106588</v>
+        <v>7106375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,12 +1283,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1303,32 +1299,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126868496</v>
+        <v>126862876</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691941</v>
+        <v>691847</v>
       </c>
       <c r="R8" t="n">
-        <v>7106860</v>
+        <v>7106392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,12 +1384,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,32 +1400,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126865523</v>
+        <v>126862884</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1435,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691797</v>
+        <v>691817</v>
       </c>
       <c r="R9" t="n">
-        <v>7106375</v>
+        <v>7106456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,12 +1485,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1505,45 +1501,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126862876</v>
+        <v>126867049</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>92616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691847</v>
+        <v>691961</v>
       </c>
       <c r="R10" t="n">
-        <v>7106392</v>
+        <v>7106020</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,18 +1583,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1606,32 +1606,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126862884</v>
+        <v>126867602</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691817</v>
+        <v>691670</v>
       </c>
       <c r="R11" t="n">
-        <v>7106456</v>
+        <v>7106776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,12 +1691,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1707,10 +1707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126862178</v>
+        <v>126867612</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1718,42 +1718,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691990</v>
+        <v>691700</v>
       </c>
       <c r="R12" t="n">
-        <v>7106753</v>
+        <v>7106739</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,12 +1792,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1816,45 +1808,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126867682</v>
+        <v>126862178</v>
       </c>
       <c r="B13" t="n">
-        <v>92616</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691980</v>
+        <v>691990</v>
       </c>
       <c r="R13" t="n">
-        <v>7106156</v>
+        <v>7106753</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1901,12 +1901,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1917,32 +1917,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126867612</v>
+        <v>126867682</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691700</v>
+        <v>691980</v>
       </c>
       <c r="R14" t="n">
-        <v>7106739</v>
+        <v>7106156</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862877</v>
+        <v>126862867</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691827</v>
+        <v>691830</v>
       </c>
       <c r="R17" t="n">
-        <v>7106338</v>
+        <v>7106333</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867621</v>
+        <v>126868486</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691806</v>
+        <v>691983</v>
       </c>
       <c r="R18" t="n">
-        <v>7106380</v>
+        <v>7106781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,12 +2402,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2418,32 +2418,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126862196</v>
+        <v>126852151</v>
       </c>
       <c r="B19" t="n">
-        <v>91322</v>
+        <v>79100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691978</v>
+        <v>691715</v>
       </c>
       <c r="R19" t="n">
-        <v>7106752</v>
+        <v>7105958</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,72 +2503,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126869129</v>
+        <v>126862877</v>
       </c>
       <c r="B20" t="n">
-        <v>57761</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>692001</v>
+        <v>691827</v>
       </c>
       <c r="R20" t="n">
-        <v>7106677</v>
+        <v>7106338</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2612,12 +2600,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2835,10 +2823,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126862867</v>
+        <v>126867621</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,21 +2834,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2870,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691830</v>
+        <v>691806</v>
       </c>
       <c r="R23" t="n">
-        <v>7106333</v>
+        <v>7106380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,12 +2908,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2936,10 +2924,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126868486</v>
+        <v>126862196</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>91322</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,21 +2935,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2971,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691983</v>
+        <v>691978</v>
       </c>
       <c r="R24" t="n">
-        <v>7106781</v>
+        <v>7106752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,12 +3009,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3037,10 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126852151</v>
+        <v>126869129</v>
       </c>
       <c r="B25" t="n">
-        <v>79100</v>
+        <v>57761</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3048,37 +3036,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6450</v>
+        <v>103031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691715</v>
+        <v>692001</v>
       </c>
       <c r="R25" t="n">
-        <v>7105958</v>
+        <v>7106677</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3122,22 +3118,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126867630</v>
+        <v>126868442</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,34 +3145,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691829</v>
+        <v>691999</v>
       </c>
       <c r="R26" t="n">
-        <v>7106294</v>
+        <v>7106730</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,12 +3223,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3235,7 +3239,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868327</v>
+        <v>126867630</v>
       </c>
       <c r="B27" t="n">
         <v>79014</v>
@@ -3270,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691816</v>
+        <v>691829</v>
       </c>
       <c r="R27" t="n">
-        <v>7106553</v>
+        <v>7106294</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,11 +3312,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3325,12 +3324,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3341,10 +3340,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868483</v>
+        <v>126868327</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3352,21 +3351,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3375,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691825</v>
+        <v>691816</v>
       </c>
       <c r="R28" t="n">
-        <v>7106330</v>
+        <v>7106553</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3416,7 +3415,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På äldre tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3431,12 +3430,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3447,7 +3446,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126859325</v>
+        <v>126868483</v>
       </c>
       <c r="B29" t="n">
         <v>80117</v>
@@ -3482,10 +3481,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691835</v>
+        <v>691825</v>
       </c>
       <c r="R29" t="n">
-        <v>7106328</v>
+        <v>7106330</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3520,6 +3519,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3532,44 +3536,48 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126862881</v>
+        <v>126859325</v>
       </c>
       <c r="B30" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3579,10 +3587,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691808</v>
+        <v>691835</v>
       </c>
       <c r="R30" t="n">
-        <v>7106575</v>
+        <v>7106328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3629,65 +3637,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126868442</v>
+        <v>126862881</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691999</v>
+        <v>691808</v>
       </c>
       <c r="R31" t="n">
-        <v>7106730</v>
+        <v>7106575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,12 +3734,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126868484</v>
+        <v>126867616</v>
       </c>
       <c r="B37" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691825</v>
+        <v>691811</v>
       </c>
       <c r="R37" t="n">
-        <v>7106372</v>
+        <v>7106492</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4328,11 +4328,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4345,12 +4340,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4361,7 +4356,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126867603</v>
+        <v>126868484</v>
       </c>
       <c r="B38" t="n">
         <v>80117</v>
@@ -4396,10 +4391,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691608</v>
+        <v>691825</v>
       </c>
       <c r="R38" t="n">
-        <v>7106686</v>
+        <v>7106372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,6 +4429,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4446,12 +4446,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4462,7 +4462,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126865524</v>
+        <v>126867603</v>
       </c>
       <c r="B39" t="n">
         <v>80117</v>
@@ -4497,10 +4497,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691833</v>
+        <v>691608</v>
       </c>
       <c r="R39" t="n">
-        <v>7106306</v>
+        <v>7106686</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4547,12 +4547,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4563,10 +4563,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126868466</v>
+        <v>126865524</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>80117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4574,21 +4574,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>692151</v>
+        <v>691833</v>
       </c>
       <c r="R40" t="n">
-        <v>7106586</v>
+        <v>7106306</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4648,12 +4648,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126862895</v>
+        <v>126862878</v>
       </c>
       <c r="B41" t="n">
-        <v>91900</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4675,21 +4675,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691850</v>
+        <v>691869</v>
       </c>
       <c r="R41" t="n">
-        <v>7106258</v>
+        <v>7106348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4765,32 +4765,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862878</v>
+        <v>126868466</v>
       </c>
       <c r="B42" t="n">
-        <v>98443</v>
+        <v>79046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691869</v>
+        <v>692151</v>
       </c>
       <c r="R42" t="n">
-        <v>7106348</v>
+        <v>7106586</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,12 +4850,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4866,32 +4866,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126868311</v>
+        <v>126862895</v>
       </c>
       <c r="B43" t="n">
-        <v>98464</v>
+        <v>91900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>760</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691808</v>
+        <v>691850</v>
       </c>
       <c r="R43" t="n">
-        <v>7106373</v>
+        <v>7106258</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,11 +4939,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Sex blommor</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4956,12 +4951,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4972,32 +4967,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126867616</v>
+        <v>126868311</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>98464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691811</v>
+        <v>691808</v>
       </c>
       <c r="R44" t="n">
-        <v>7106492</v>
+        <v>7106373</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,6 +5040,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sex blommor</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5057,12 +5057,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5073,10 +5073,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126868309</v>
+        <v>126868333</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>92616</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5084,21 +5084,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5108,10 +5108,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691829</v>
+        <v>691786</v>
       </c>
       <c r="R45" t="n">
-        <v>7106310</v>
+        <v>7106584</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5174,45 +5174,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126868333</v>
+        <v>126865683</v>
       </c>
       <c r="B46" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691786</v>
+        <v>691713</v>
       </c>
       <c r="R46" t="n">
-        <v>7106584</v>
+        <v>7105959</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5253,18 +5256,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5275,48 +5279,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126865683</v>
+        <v>126868309</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691713</v>
+        <v>691829</v>
       </c>
       <c r="R47" t="n">
-        <v>7105959</v>
+        <v>7106310</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5357,19 +5358,18 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -7740,10 +7740,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126862873</v>
+        <v>126867617</v>
       </c>
       <c r="B71" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7751,21 +7751,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>691721</v>
+        <v>691814</v>
       </c>
       <c r="R71" t="n">
-        <v>7105960</v>
+        <v>7106474</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7825,12 +7825,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7841,10 +7841,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126862855</v>
+        <v>126862873</v>
       </c>
       <c r="B72" t="n">
-        <v>79632</v>
+        <v>78772</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7852,21 +7852,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7942,32 +7942,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126862874</v>
+        <v>126862855</v>
       </c>
       <c r="B73" t="n">
-        <v>98443</v>
+        <v>79632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>691824</v>
+        <v>691721</v>
       </c>
       <c r="R73" t="n">
-        <v>7106450</v>
+        <v>7105960</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8043,32 +8043,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126867617</v>
+        <v>126862874</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>691814</v>
+        <v>691824</v>
       </c>
       <c r="R74" t="n">
-        <v>7106474</v>
+        <v>7106450</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8128,12 +8128,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -11515,32 +11515,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126862890</v>
+        <v>126868314</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>691859</v>
+        <v>691991</v>
       </c>
       <c r="R108" t="n">
-        <v>7106523</v>
+        <v>7106099</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11600,12 +11600,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11616,10 +11616,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126869123</v>
+        <v>126867610</v>
       </c>
       <c r="B109" t="n">
-        <v>79046</v>
+        <v>78772</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11627,37 +11627,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>691917</v>
+        <v>691783</v>
       </c>
       <c r="R109" t="n">
-        <v>7106857</v>
+        <v>7106563</v>
       </c>
       <c r="S109" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11701,12 +11701,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11717,32 +11717,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126868314</v>
+        <v>126852645</v>
       </c>
       <c r="B110" t="n">
-        <v>97327</v>
+        <v>78772</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11752,10 +11752,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>691991</v>
+        <v>691715</v>
       </c>
       <c r="R110" t="n">
-        <v>7106099</v>
+        <v>7105958</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11802,19 +11802,15 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11919,10 +11915,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126867610</v>
+        <v>126862890</v>
       </c>
       <c r="B112" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11930,21 +11926,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11954,10 +11950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>691783</v>
+        <v>691859</v>
       </c>
       <c r="R112" t="n">
-        <v>7106563</v>
+        <v>7106523</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12004,12 +12000,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12020,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126852645</v>
+        <v>126869123</v>
       </c>
       <c r="B113" t="n">
-        <v>78772</v>
+        <v>79046</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12031,37 +12027,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>691715</v>
+        <v>691917</v>
       </c>
       <c r="R113" t="n">
-        <v>7105958</v>
+        <v>7106857</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12105,15 +12101,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14066,45 +14066,61 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126867655</v>
+        <v>126862860</v>
       </c>
       <c r="B133" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691840</v>
+        <v>691767</v>
       </c>
       <c r="R133" t="n">
-        <v>7105751</v>
+        <v>7105824</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14139,6 +14155,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Höna med kyckling</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14151,12 +14172,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14167,10 +14188,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126862860</v>
+        <v>126868338</v>
       </c>
       <c r="B134" t="n">
-        <v>56849</v>
+        <v>92616</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14178,50 +14199,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691767</v>
+        <v>691750</v>
       </c>
       <c r="R134" t="n">
-        <v>7105824</v>
+        <v>7105871</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14258,7 +14263,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Höna med kyckling</t>
+          <t>Tre g:a fk.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14273,12 +14278,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14289,32 +14294,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126868338</v>
+        <v>126867655</v>
       </c>
       <c r="B135" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14324,10 +14329,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691750</v>
+        <v>691840</v>
       </c>
       <c r="R135" t="n">
-        <v>7105871</v>
+        <v>7105751</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14362,11 +14367,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Tre g:a fk.</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14379,12 +14379,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14699,32 +14699,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126868475</v>
+        <v>126863145</v>
       </c>
       <c r="B139" t="n">
-        <v>58488</v>
+        <v>79603</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208245</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691770</v>
+        <v>691819</v>
       </c>
       <c r="R139" t="n">
-        <v>7105834</v>
+        <v>7105865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14784,12 +14784,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14800,32 +14800,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126863145</v>
+        <v>126868475</v>
       </c>
       <c r="B140" t="n">
-        <v>79603</v>
+        <v>58488</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>208245</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14835,10 +14835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691819</v>
+        <v>691770</v>
       </c>
       <c r="R140" t="n">
-        <v>7105865</v>
+        <v>7105834</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14885,12 +14885,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15507,10 +15507,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126862172</v>
+        <v>126862181</v>
       </c>
       <c r="B147" t="n">
-        <v>91326</v>
+        <v>78773</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15518,21 +15518,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15542,10 +15542,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691876</v>
+        <v>691865</v>
       </c>
       <c r="R147" t="n">
-        <v>7105714</v>
+        <v>7105739</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15608,10 +15608,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126862181</v>
+        <v>126862172</v>
       </c>
       <c r="B148" t="n">
-        <v>78773</v>
+        <v>91326</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15619,21 +15619,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>691865</v>
+        <v>691876</v>
       </c>
       <c r="R148" t="n">
-        <v>7105739</v>
+        <v>7105714</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15709,10 +15709,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126868305</v>
+        <v>126867670</v>
       </c>
       <c r="B149" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15720,21 +15720,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>691870</v>
+        <v>691697</v>
       </c>
       <c r="R149" t="n">
-        <v>7105761</v>
+        <v>7105917</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15794,12 +15794,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15810,7 +15810,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126867670</v>
+        <v>126867659</v>
       </c>
       <c r="B150" t="n">
         <v>79014</v>
@@ -15845,10 +15845,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>691697</v>
+        <v>691800</v>
       </c>
       <c r="R150" t="n">
-        <v>7105917</v>
+        <v>7105765</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15911,7 +15911,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126867659</v>
+        <v>126862471</v>
       </c>
       <c r="B151" t="n">
         <v>79014</v>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691800</v>
+        <v>691883</v>
       </c>
       <c r="R151" t="n">
-        <v>7105765</v>
+        <v>7105746</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15996,26 +15996,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY151" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126862471</v>
+        <v>126868305</v>
       </c>
       <c r="B152" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16023,21 +16019,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16047,10 +16043,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691883</v>
+        <v>691870</v>
       </c>
       <c r="R152" t="n">
-        <v>7105746</v>
+        <v>7105761</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16097,15 +16093,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16725,53 +16725,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126862188</v>
+        <v>126868303</v>
       </c>
       <c r="B159" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691721</v>
+        <v>691875</v>
       </c>
       <c r="R159" t="n">
-        <v>7105882</v>
+        <v>7105775</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16818,12 +16810,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16834,45 +16826,53 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126868303</v>
+        <v>126862188</v>
       </c>
       <c r="B160" t="n">
-        <v>79632</v>
+        <v>58027</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>103015</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691875</v>
+        <v>691721</v>
       </c>
       <c r="R160" t="n">
-        <v>7105775</v>
+        <v>7105882</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16919,12 +16919,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17036,45 +17036,57 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126851600</v>
+        <v>126862207</v>
       </c>
       <c r="B162" t="n">
-        <v>80021</v>
+        <v>57657</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691807</v>
+        <v>691872</v>
       </c>
       <c r="R162" t="n">
-        <v>7105857</v>
+        <v>7105752</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17121,22 +17133,26 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126862171</v>
+        <v>126867676</v>
       </c>
       <c r="B163" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17144,21 +17160,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17168,10 +17184,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691772</v>
+        <v>691698</v>
       </c>
       <c r="R163" t="n">
-        <v>7105843</v>
+        <v>7105935</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17218,12 +17234,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17234,27 +17250,27 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126862207</v>
+        <v>126862468</v>
       </c>
       <c r="B164" t="n">
-        <v>57657</v>
+        <v>58027</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -17262,29 +17278,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>691872</v>
+        <v>691726</v>
       </c>
       <c r="R164" t="n">
-        <v>7105752</v>
+        <v>7105895</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17331,48 +17335,44 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126867676</v>
+        <v>126851600</v>
       </c>
       <c r="B165" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17382,10 +17382,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>691698</v>
+        <v>691807</v>
       </c>
       <c r="R165" t="n">
-        <v>7105935</v>
+        <v>7105857</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17432,48 +17432,44 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126862468</v>
+        <v>126862171</v>
       </c>
       <c r="B166" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17483,10 +17479,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>691726</v>
+        <v>691772</v>
       </c>
       <c r="R166" t="n">
-        <v>7105895</v>
+        <v>7105843</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17533,15 +17529,19 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19088,10 +19088,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126866170</v>
+        <v>126867661</v>
       </c>
       <c r="B182" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19099,37 +19099,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>691883</v>
+        <v>691743</v>
       </c>
       <c r="R182" t="n">
-        <v>7105912</v>
+        <v>7105870</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19170,19 +19167,18 @@
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19193,45 +19189,48 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126862871</v>
+        <v>126866170</v>
       </c>
       <c r="B183" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>691713</v>
+        <v>691883</v>
       </c>
       <c r="R183" t="n">
-        <v>7105893</v>
+        <v>7105912</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19272,18 +19271,19 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19400,32 +19400,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126867661</v>
+        <v>126862871</v>
       </c>
       <c r="B185" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19435,10 +19435,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>691743</v>
+        <v>691713</v>
       </c>
       <c r="R185" t="n">
-        <v>7105870</v>
+        <v>7105893</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19485,12 +19485,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -20407,10 +20407,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126862180</v>
+        <v>126868499</v>
       </c>
       <c r="B195" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -20418,21 +20418,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20442,10 +20442,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>692178</v>
+        <v>691849</v>
       </c>
       <c r="R195" t="n">
-        <v>7107022</v>
+        <v>7106968</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20480,6 +20480,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -20492,12 +20497,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
@@ -20508,10 +20513,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126863150</v>
+        <v>126855647</v>
       </c>
       <c r="B196" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20519,21 +20524,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20543,10 +20548,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>693008</v>
+        <v>692383</v>
       </c>
       <c r="R196" t="n">
-        <v>7105846</v>
+        <v>7106365</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20593,61 +20598,61 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126868499</v>
+        <v>126868471</v>
       </c>
       <c r="B197" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691849</v>
+        <v>692149</v>
       </c>
       <c r="R197" t="n">
-        <v>7106968</v>
+        <v>7106995</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20684,7 +20689,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20715,10 +20720,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126855647</v>
+        <v>126868478</v>
       </c>
       <c r="B198" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -20726,21 +20731,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20750,10 +20755,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>692383</v>
+        <v>692202</v>
       </c>
       <c r="R198" t="n">
-        <v>7106365</v>
+        <v>7106954</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20800,61 +20805,61 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY198" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126868471</v>
+        <v>126862180</v>
       </c>
       <c r="B199" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>692149</v>
+        <v>692178</v>
       </c>
       <c r="R199" t="n">
-        <v>7106995</v>
+        <v>7107022</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20889,11 +20894,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
@@ -20906,12 +20906,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -20922,7 +20922,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126868478</v>
+        <v>126863150</v>
       </c>
       <c r="B200" t="n">
         <v>78773</v>
@@ -20957,10 +20957,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>692202</v>
+        <v>693008</v>
       </c>
       <c r="R200" t="n">
-        <v>7106954</v>
+        <v>7105846</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21007,12 +21007,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -21124,10 +21124,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126867504</v>
+        <v>126868468</v>
       </c>
       <c r="B202" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -21135,37 +21135,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>692384</v>
+        <v>692246</v>
       </c>
       <c r="R202" t="n">
-        <v>7106387</v>
+        <v>7106895</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21206,19 +21203,18 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -21229,10 +21225,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126868468</v>
+        <v>126867504</v>
       </c>
       <c r="B203" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21240,34 +21236,37 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>692246</v>
+        <v>692384</v>
       </c>
       <c r="R203" t="n">
-        <v>7106895</v>
+        <v>7106387</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21308,18 +21307,19 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -22647,10 +22647,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126862190</v>
+        <v>126863148</v>
       </c>
       <c r="B217" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -22658,21 +22658,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22682,10 +22682,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>692155</v>
+        <v>693009</v>
       </c>
       <c r="R217" t="n">
-        <v>7107055</v>
+        <v>7105804</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22732,12 +22732,12 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
@@ -22748,10 +22748,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>126862179</v>
+        <v>126862190</v>
       </c>
       <c r="B218" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -22759,21 +22759,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22783,10 +22783,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>692087</v>
+        <v>692155</v>
       </c>
       <c r="R218" t="n">
-        <v>7107184</v>
+        <v>7107055</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22849,10 +22849,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>126863144</v>
+        <v>126862179</v>
       </c>
       <c r="B219" t="n">
-        <v>79603</v>
+        <v>78773</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -22860,21 +22860,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22884,10 +22884,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>692913</v>
+        <v>692087</v>
       </c>
       <c r="R219" t="n">
-        <v>7105995</v>
+        <v>7107184</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22934,12 +22934,12 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
@@ -22950,10 +22950,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>126863148</v>
+        <v>126863144</v>
       </c>
       <c r="B220" t="n">
-        <v>78773</v>
+        <v>79603</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -22961,21 +22961,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22985,10 +22985,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>693009</v>
+        <v>692913</v>
       </c>
       <c r="R220" t="n">
-        <v>7105804</v>
+        <v>7105995</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -996,45 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126865523</v>
+        <v>126867049</v>
       </c>
       <c r="B5" t="n">
-        <v>80117</v>
+        <v>92616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691797</v>
+        <v>691961</v>
       </c>
       <c r="R5" t="n">
-        <v>7106375</v>
+        <v>7106020</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,18 +1078,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1097,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126868503</v>
+        <v>126865523</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692149</v>
+        <v>691797</v>
       </c>
       <c r="R6" t="n">
-        <v>7106588</v>
+        <v>7106375</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,12 +1186,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1198,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868496</v>
+        <v>126868503</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1233,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691941</v>
+        <v>692149</v>
       </c>
       <c r="R7" t="n">
-        <v>7106860</v>
+        <v>7106588</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,48 +1303,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126867049</v>
+        <v>126868496</v>
       </c>
       <c r="B8" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691961</v>
+        <v>691941</v>
       </c>
       <c r="R8" t="n">
-        <v>7106020</v>
+        <v>7106860</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,19 +1382,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,32 +1404,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126867602</v>
+        <v>126862876</v>
       </c>
       <c r="B9" t="n">
-        <v>78773</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691670</v>
+        <v>691847</v>
       </c>
       <c r="R9" t="n">
-        <v>7106776</v>
+        <v>7106392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,12 +1489,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1505,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126862876</v>
+        <v>126862884</v>
       </c>
       <c r="B10" t="n">
         <v>98443</v>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691847</v>
+        <v>691817</v>
       </c>
       <c r="R10" t="n">
-        <v>7106392</v>
+        <v>7106456</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,32 +1606,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126862884</v>
+        <v>126867602</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691817</v>
+        <v>691670</v>
       </c>
       <c r="R11" t="n">
-        <v>7106456</v>
+        <v>7106776</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,12 +1691,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -3240,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868442</v>
+        <v>126868483</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,38 +3251,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691999</v>
+        <v>691825</v>
       </c>
       <c r="R27" t="n">
-        <v>7106730</v>
+        <v>7106330</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3317,6 +3313,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3329,12 +3330,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3345,7 +3346,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868483</v>
+        <v>126859325</v>
       </c>
       <c r="B28" t="n">
         <v>80117</v>
@@ -3380,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691825</v>
+        <v>691835</v>
       </c>
       <c r="R28" t="n">
-        <v>7106330</v>
+        <v>7106328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3418,11 +3419,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3435,26 +3431,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126859325</v>
+        <v>126867630</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3462,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3486,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691835</v>
+        <v>691829</v>
       </c>
       <c r="R29" t="n">
-        <v>7106328</v>
+        <v>7106294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3536,22 +3528,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126867630</v>
+        <v>126868442</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,34 +3555,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691829</v>
+        <v>691999</v>
       </c>
       <c r="R30" t="n">
-        <v>7106294</v>
+        <v>7106730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,12 +3633,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3750,32 +3750,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126867684</v>
+        <v>126852734</v>
       </c>
       <c r="B32" t="n">
-        <v>92616</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691963</v>
+        <v>691715</v>
       </c>
       <c r="R32" t="n">
-        <v>7106099</v>
+        <v>7105958</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3835,26 +3835,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126867640</v>
+        <v>126862866</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3862,21 +3858,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691978</v>
+        <v>691721</v>
       </c>
       <c r="R33" t="n">
-        <v>7106086</v>
+        <v>7105960</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3936,12 +3932,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3952,7 +3948,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126852734</v>
+        <v>126867833</v>
       </c>
       <c r="B34" t="n">
         <v>78773</v>
@@ -3981,16 +3977,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691715</v>
+        <v>692199</v>
       </c>
       <c r="R34" t="n">
-        <v>7105958</v>
+        <v>7106891</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4031,50 +4030,55 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126862866</v>
+        <v>126867684</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>92616</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4084,10 +4088,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691721</v>
+        <v>691963</v>
       </c>
       <c r="R35" t="n">
-        <v>7105960</v>
+        <v>7106099</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4134,12 +4138,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4150,10 +4154,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126867833</v>
+        <v>126867640</v>
       </c>
       <c r="B36" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4161,37 +4165,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>692199</v>
+        <v>691978</v>
       </c>
       <c r="R36" t="n">
-        <v>7106891</v>
+        <v>7106086</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4232,19 +4233,18 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -5486,32 +5486,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126867680</v>
+        <v>126867609</v>
       </c>
       <c r="B49" t="n">
-        <v>92616</v>
+        <v>78772</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691998</v>
+        <v>691764</v>
       </c>
       <c r="R49" t="n">
-        <v>7106190</v>
+        <v>7106568</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126868092</v>
+        <v>126868489</v>
       </c>
       <c r="B50" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5598,37 +5598,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691959</v>
+        <v>691831</v>
       </c>
       <c r="R50" t="n">
-        <v>7106774</v>
+        <v>7106328</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5669,19 +5666,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5692,10 +5688,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862868</v>
+        <v>126862888</v>
       </c>
       <c r="B51" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5703,21 +5699,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5727,10 +5723,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691831</v>
+        <v>691826</v>
       </c>
       <c r="R51" t="n">
-        <v>7106374</v>
+        <v>7106492</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5793,32 +5789,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126867609</v>
+        <v>126867680</v>
       </c>
       <c r="B52" t="n">
-        <v>78772</v>
+        <v>92616</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691764</v>
+        <v>691998</v>
       </c>
       <c r="R52" t="n">
-        <v>7106568</v>
+        <v>7106190</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5894,10 +5890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126868489</v>
+        <v>126868092</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5905,34 +5901,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691831</v>
+        <v>691959</v>
       </c>
       <c r="R53" t="n">
-        <v>7106328</v>
+        <v>7106774</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5973,18 +5972,19 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5995,10 +5995,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126862888</v>
+        <v>126862868</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691826</v>
+        <v>691831</v>
       </c>
       <c r="R54" t="n">
-        <v>7106492</v>
+        <v>7106374</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126868316</v>
+        <v>126868320</v>
       </c>
       <c r="B61" t="n">
         <v>80117</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691796</v>
+        <v>691833</v>
       </c>
       <c r="R61" t="n">
-        <v>7106376</v>
+        <v>7106302</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt gammal sälg intill hyggeskant.</t>
+          <t>Rikligt gammal grövre sälg.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,32 +6808,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126867592</v>
+        <v>126868316</v>
       </c>
       <c r="B62" t="n">
-        <v>79038</v>
+        <v>80117</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691747</v>
+        <v>691796</v>
       </c>
       <c r="R62" t="n">
-        <v>7106703</v>
+        <v>7106376</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6881,6 +6881,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt gammal sälg intill hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6893,12 +6898,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6909,32 +6914,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126867623</v>
+        <v>126867592</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,10 +6949,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691797</v>
+        <v>691747</v>
       </c>
       <c r="R63" t="n">
-        <v>7106341</v>
+        <v>7106703</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7010,7 +7015,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126862892</v>
+        <v>126867623</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7045,10 +7050,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>691871</v>
+        <v>691797</v>
       </c>
       <c r="R64" t="n">
-        <v>7106324</v>
+        <v>7106341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7095,12 +7100,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7111,10 +7116,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126862176</v>
+        <v>126862892</v>
       </c>
       <c r="B65" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7122,42 +7127,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>692001</v>
+        <v>691871</v>
       </c>
       <c r="R65" t="n">
-        <v>7106695</v>
+        <v>7106324</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7204,12 +7201,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7220,10 +7217,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126867634</v>
+        <v>126862176</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7231,34 +7228,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691888</v>
+        <v>692001</v>
       </c>
       <c r="R66" t="n">
-        <v>7106163</v>
+        <v>7106695</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,12 +7310,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7321,32 +7326,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126868328</v>
+        <v>126865528</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7356,10 +7361,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691816</v>
+        <v>691813</v>
       </c>
       <c r="R67" t="n">
-        <v>7106552</v>
+        <v>7106581</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7394,11 +7399,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7411,12 +7411,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7427,32 +7427,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126868320</v>
+        <v>126868488</v>
       </c>
       <c r="B68" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691833</v>
+        <v>691828</v>
       </c>
       <c r="R68" t="n">
-        <v>7106302</v>
+        <v>7106415</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt gammal grövre sälg.</t>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7517,12 +7517,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7533,32 +7533,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126865528</v>
+        <v>126867634</v>
       </c>
       <c r="B69" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691813</v>
+        <v>691888</v>
       </c>
       <c r="R69" t="n">
-        <v>7106581</v>
+        <v>7106163</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7618,12 +7618,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7634,32 +7634,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126868488</v>
+        <v>126868328</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>691828</v>
+        <v>691816</v>
       </c>
       <c r="R70" t="n">
-        <v>7106415</v>
+        <v>7106552</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Blommande</t>
+          <t>På äldre tall.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7724,12 +7724,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8245,32 +8245,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126862883</v>
+        <v>126867613</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>691832</v>
+        <v>691720</v>
       </c>
       <c r="R76" t="n">
-        <v>7106475</v>
+        <v>7106626</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,12 +8330,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8346,7 +8346,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126867625</v>
+        <v>126867636</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>691792</v>
+        <v>691954</v>
       </c>
       <c r="R77" t="n">
-        <v>7106323</v>
+        <v>7106198</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126868317</v>
+        <v>126867625</v>
       </c>
       <c r="B78" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8458,21 +8458,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>691833</v>
+        <v>691792</v>
       </c>
       <c r="R78" t="n">
-        <v>7106362</v>
+        <v>7106323</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8520,11 +8520,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På  "sälg låga".</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8537,12 +8532,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8553,7 +8548,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126865527</v>
+        <v>126868317</v>
       </c>
       <c r="B79" t="n">
         <v>80117</v>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>691852</v>
+        <v>691833</v>
       </c>
       <c r="R79" t="n">
-        <v>7106251</v>
+        <v>7106362</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8626,6 +8621,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På  "sälg låga".</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8638,12 +8638,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126868507</v>
+        <v>126865527</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>691973</v>
+        <v>691852</v>
       </c>
       <c r="R80" t="n">
-        <v>7106021</v>
+        <v>7106251</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8739,12 +8739,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8755,7 +8755,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126867613</v>
+        <v>126868507</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>691720</v>
+        <v>691973</v>
       </c>
       <c r="R81" t="n">
-        <v>7106626</v>
+        <v>7106021</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,12 +8840,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126867636</v>
+        <v>126862883</v>
       </c>
       <c r="B82" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>691954</v>
+        <v>691832</v>
       </c>
       <c r="R82" t="n">
-        <v>7106198</v>
+        <v>7106475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8941,12 +8941,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -10108,32 +10108,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126868308</v>
+        <v>126862894</v>
       </c>
       <c r="B94" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10143,10 +10143,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>691838</v>
+        <v>692038</v>
       </c>
       <c r="R94" t="n">
-        <v>7106314</v>
+        <v>7106130</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10193,12 +10193,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10209,32 +10209,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126862894</v>
+        <v>126867593</v>
       </c>
       <c r="B95" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>692038</v>
+        <v>691804</v>
       </c>
       <c r="R95" t="n">
-        <v>7106130</v>
+        <v>7106502</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10294,12 +10294,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10310,10 +10310,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126867593</v>
+        <v>126868308</v>
       </c>
       <c r="B96" t="n">
-        <v>79038</v>
+        <v>80146</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10321,21 +10321,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>691804</v>
+        <v>691838</v>
       </c>
       <c r="R96" t="n">
-        <v>7106502</v>
+        <v>7106314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10395,12 +10395,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11220,10 +11220,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126852559</v>
+        <v>126862889</v>
       </c>
       <c r="B105" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11231,21 +11231,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11255,10 +11255,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>691715</v>
+        <v>691769</v>
       </c>
       <c r="R105" t="n">
-        <v>7105958</v>
+        <v>7106636</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,22 +11305,26 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Isac Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126862889</v>
+        <v>126852559</v>
       </c>
       <c r="B106" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11328,21 +11332,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11352,10 +11356,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>691769</v>
+        <v>691715</v>
       </c>
       <c r="R106" t="n">
-        <v>7106636</v>
+        <v>7105958</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11402,19 +11406,15 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11515,10 +11515,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126867610</v>
+        <v>126869123</v>
       </c>
       <c r="B108" t="n">
-        <v>78772</v>
+        <v>79046</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11526,37 +11526,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>691783</v>
+        <v>691917</v>
       </c>
       <c r="R108" t="n">
-        <v>7106563</v>
+        <v>7106857</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11600,12 +11600,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11616,10 +11616,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126852645</v>
+        <v>126867638</v>
       </c>
       <c r="B109" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11627,21 +11627,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>691715</v>
+        <v>691977</v>
       </c>
       <c r="R109" t="n">
-        <v>7105958</v>
+        <v>7106091</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11701,22 +11701,26 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126862890</v>
+        <v>126867610</v>
       </c>
       <c r="B110" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11724,21 +11728,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11748,10 +11752,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>691859</v>
+        <v>691783</v>
       </c>
       <c r="R110" t="n">
-        <v>7106523</v>
+        <v>7106563</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11798,12 +11802,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11814,32 +11818,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126868314</v>
+        <v>126852645</v>
       </c>
       <c r="B111" t="n">
-        <v>97327</v>
+        <v>78772</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11849,10 +11853,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>691991</v>
+        <v>691715</v>
       </c>
       <c r="R111" t="n">
-        <v>7106099</v>
+        <v>7105958</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11899,26 +11903,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126869123</v>
+        <v>126862890</v>
       </c>
       <c r="B112" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11926,37 +11926,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>691917</v>
+        <v>691859</v>
       </c>
       <c r="R112" t="n">
-        <v>7106857</v>
+        <v>7106523</v>
       </c>
       <c r="S112" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12000,12 +12000,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12016,32 +12016,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126867638</v>
+        <v>126868314</v>
       </c>
       <c r="B113" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>691977</v>
+        <v>691991</v>
       </c>
       <c r="R113" t="n">
-        <v>7106091</v>
+        <v>7106099</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12101,12 +12101,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12117,7 +12117,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126868493</v>
+        <v>126867632</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>691997</v>
+        <v>691815</v>
       </c>
       <c r="R114" t="n">
-        <v>7106738</v>
+        <v>7106269</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,12 +12202,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12218,7 +12218,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126867614</v>
+        <v>126868493</v>
       </c>
       <c r="B115" t="n">
         <v>79014</v>
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>691757</v>
+        <v>691997</v>
       </c>
       <c r="R115" t="n">
-        <v>7106584</v>
+        <v>7106738</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12303,12 +12303,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12319,27 +12319,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126856407</v>
+        <v>126867614</v>
       </c>
       <c r="B116" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>692211</v>
+        <v>691757</v>
       </c>
       <c r="R116" t="n">
-        <v>7106863</v>
+        <v>7106584</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12404,44 +12404,48 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126868325</v>
+        <v>126856407</v>
       </c>
       <c r="B117" t="n">
-        <v>98443</v>
+        <v>80152</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12451,10 +12455,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>691824</v>
+        <v>692211</v>
       </c>
       <c r="R117" t="n">
-        <v>7106438</v>
+        <v>7106863</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12489,11 +12493,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>1 blomma.</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12506,26 +12505,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126867632</v>
+        <v>126862177</v>
       </c>
       <c r="B118" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12533,34 +12528,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>691815</v>
+        <v>692018</v>
       </c>
       <c r="R118" t="n">
-        <v>7106269</v>
+        <v>7106688</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12607,12 +12610,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12623,53 +12626,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126862177</v>
+        <v>126868325</v>
       </c>
       <c r="B119" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>692018</v>
+        <v>691824</v>
       </c>
       <c r="R119" t="n">
-        <v>7106688</v>
+        <v>7106438</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12704,6 +12699,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>1 blomma.</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12716,12 +12716,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12732,10 +12732,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126868494</v>
+        <v>126868318</v>
       </c>
       <c r="B120" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12743,21 +12743,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>691985</v>
+        <v>691844</v>
       </c>
       <c r="R120" t="n">
-        <v>7106752</v>
+        <v>7106329</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12805,6 +12805,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
@@ -12817,12 +12822,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12833,32 +12838,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126868497</v>
+        <v>126868473</v>
       </c>
       <c r="B121" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12868,10 +12873,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>691928</v>
+        <v>691977</v>
       </c>
       <c r="R121" t="n">
-        <v>7106864</v>
+        <v>7106779</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12906,17 +12911,13 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På gammal grov gran</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -12939,45 +12940,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126868318</v>
+        <v>126862191</v>
       </c>
       <c r="B122" t="n">
-        <v>80117</v>
+        <v>98443</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>691844</v>
+        <v>691819</v>
       </c>
       <c r="R122" t="n">
-        <v>7106329</v>
+        <v>7106338</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13012,29 +13017,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13045,32 +13046,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126868464</v>
+        <v>126868326</v>
       </c>
       <c r="B123" t="n">
-        <v>75138</v>
+        <v>98443</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13080,10 +13081,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>692154</v>
+        <v>691820</v>
       </c>
       <c r="R123" t="n">
-        <v>7106591</v>
+        <v>7106411</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13118,6 +13119,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -13130,12 +13136,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -13146,32 +13152,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126867594</v>
+        <v>126862886</v>
       </c>
       <c r="B124" t="n">
-        <v>79038</v>
+        <v>98443</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6434</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13181,10 +13187,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691827</v>
+        <v>691817</v>
       </c>
       <c r="R124" t="n">
-        <v>7106280</v>
+        <v>7106463</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13231,12 +13237,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13247,32 +13253,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126868473</v>
+        <v>126868494</v>
       </c>
       <c r="B125" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13282,10 +13288,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>691977</v>
+        <v>691985</v>
       </c>
       <c r="R125" t="n">
-        <v>7106779</v>
+        <v>7106752</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13326,7 +13332,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -13349,49 +13354,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126862191</v>
+        <v>126868497</v>
       </c>
       <c r="B126" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>691819</v>
+        <v>691928</v>
       </c>
       <c r="R126" t="n">
-        <v>7106338</v>
+        <v>7106864</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13426,25 +13427,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>På gammal grov gran</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13455,32 +13460,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126868326</v>
+        <v>126868464</v>
       </c>
       <c r="B127" t="n">
-        <v>98443</v>
+        <v>75138</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13490,10 +13495,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691820</v>
+        <v>692154</v>
       </c>
       <c r="R127" t="n">
-        <v>7106411</v>
+        <v>7106591</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13528,11 +13533,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13545,12 +13545,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13561,32 +13561,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126862886</v>
+        <v>126867594</v>
       </c>
       <c r="B128" t="n">
-        <v>98443</v>
+        <v>79038</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13596,10 +13596,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>691817</v>
+        <v>691827</v>
       </c>
       <c r="R128" t="n">
-        <v>7106463</v>
+        <v>7106280</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13646,12 +13646,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -14395,32 +14395,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126867668</v>
+        <v>126868475</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>58488</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14430,10 +14430,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691702</v>
+        <v>691770</v>
       </c>
       <c r="R136" t="n">
-        <v>7105912</v>
+        <v>7105834</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14480,12 +14480,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14496,10 +14496,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126869124</v>
+        <v>126867668</v>
       </c>
       <c r="B137" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14507,37 +14507,37 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691841</v>
+        <v>691702</v>
       </c>
       <c r="R137" t="n">
-        <v>7105771</v>
+        <v>7105912</v>
       </c>
       <c r="S137" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14575,19 +14575,18 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14598,10 +14597,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126867652</v>
+        <v>126869124</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14609,37 +14608,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691851</v>
+        <v>691841</v>
       </c>
       <c r="R138" t="n">
-        <v>7105739</v>
+        <v>7105771</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14677,18 +14676,19 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14699,32 +14699,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126868475</v>
+        <v>126867654</v>
       </c>
       <c r="B139" t="n">
-        <v>58488</v>
+        <v>79014</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14734,10 +14734,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691770</v>
+        <v>691851</v>
       </c>
       <c r="R139" t="n">
-        <v>7105834</v>
+        <v>7105739</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14784,12 +14784,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -16619,32 +16619,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126868303</v>
+        <v>126863167</v>
       </c>
       <c r="B158" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16654,10 +16654,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691875</v>
+        <v>691825</v>
       </c>
       <c r="R158" t="n">
-        <v>7105775</v>
+        <v>7105864</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16692,6 +16692,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ca 20-30 fjolårsexemplar</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
@@ -16704,12 +16709,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16720,53 +16725,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126862188</v>
+        <v>126868303</v>
       </c>
       <c r="B159" t="n">
-        <v>58027</v>
+        <v>79632</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691721</v>
+        <v>691875</v>
       </c>
       <c r="R159" t="n">
-        <v>7105882</v>
+        <v>7105775</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16813,12 +16810,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16829,10 +16826,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126863167</v>
+        <v>126862188</v>
       </c>
       <c r="B160" t="n">
-        <v>92616</v>
+        <v>58027</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16840,34 +16837,42 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691825</v>
+        <v>691721</v>
       </c>
       <c r="R160" t="n">
-        <v>7105864</v>
+        <v>7105882</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16902,11 +16907,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Ca 20-30 fjolårsexemplar</t>
-        </is>
-      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
@@ -16919,12 +16919,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -17545,32 +17545,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126862465</v>
+        <v>126868470</v>
       </c>
       <c r="B167" t="n">
-        <v>98464</v>
+        <v>79632</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17580,10 +17580,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691913</v>
+        <v>691906</v>
       </c>
       <c r="R167" t="n">
-        <v>7105810</v>
+        <v>7105789</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17618,11 +17618,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>&gt;10 ex</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -17635,69 +17630,61 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126862862</v>
+        <v>126862170</v>
       </c>
       <c r="B168" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691772</v>
+        <v>691866</v>
       </c>
       <c r="R168" t="n">
-        <v>7105816</v>
+        <v>7105795</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17732,11 +17719,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Flygfärdig kyckling med höna</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17749,12 +17731,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17765,45 +17747,57 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126868470</v>
+        <v>126862862</v>
       </c>
       <c r="B169" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691906</v>
+        <v>691772</v>
       </c>
       <c r="R169" t="n">
-        <v>7105789</v>
+        <v>7105816</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17838,6 +17832,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Flygfärdig kyckling med höna</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17850,12 +17849,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17866,32 +17865,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126862170</v>
+        <v>126862465</v>
       </c>
       <c r="B170" t="n">
-        <v>79632</v>
+        <v>98464</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17901,10 +17900,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691866</v>
+        <v>691913</v>
       </c>
       <c r="R170" t="n">
-        <v>7105795</v>
+        <v>7105810</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17939,6 +17938,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>&gt;10 ex</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -17951,19 +17955,15 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18679,32 +18679,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126868337</v>
+        <v>126867648</v>
       </c>
       <c r="B178" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18714,10 +18714,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691763</v>
+        <v>691932</v>
       </c>
       <c r="R178" t="n">
-        <v>7105866</v>
+        <v>7105700</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18752,11 +18752,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>4 g:a fk.</t>
-        </is>
-      </c>
       <c r="AD178" t="b">
         <v>0</v>
       </c>
@@ -18769,12 +18764,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18785,32 +18780,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126867648</v>
+        <v>126868337</v>
       </c>
       <c r="B179" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18820,10 +18815,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>691932</v>
+        <v>691763</v>
       </c>
       <c r="R179" t="n">
-        <v>7105700</v>
+        <v>7105866</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18858,6 +18853,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>4 g:a fk.</t>
+        </is>
+      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18870,12 +18870,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -19088,7 +19088,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>126868508</v>
+        <v>126867661</v>
       </c>
       <c r="B182" t="n">
         <v>79014</v>
@@ -19123,10 +19123,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>691903</v>
+        <v>691743</v>
       </c>
       <c r="R182" t="n">
-        <v>7105826</v>
+        <v>7105870</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19161,11 +19161,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -19178,12 +19173,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19194,7 +19189,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>126867661</v>
+        <v>126868508</v>
       </c>
       <c r="B183" t="n">
         <v>79014</v>
@@ -19229,10 +19224,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>691743</v>
+        <v>691903</v>
       </c>
       <c r="R183" t="n">
-        <v>7105870</v>
+        <v>7105826</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19267,6 +19262,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
@@ -19279,12 +19279,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19602,48 +19602,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126867672</v>
+        <v>126869139</v>
       </c>
       <c r="B187" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>691693</v>
+        <v>691878</v>
       </c>
       <c r="R187" t="n">
-        <v>7105912</v>
+        <v>7105889</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19687,12 +19687,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -19703,32 +19703,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126862473</v>
+        <v>126867672</v>
       </c>
       <c r="B188" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19738,10 +19738,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>691699</v>
+        <v>691693</v>
       </c>
       <c r="R188" t="n">
-        <v>7105908</v>
+        <v>7105912</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19788,22 +19788,26 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126869139</v>
+        <v>126862473</v>
       </c>
       <c r="B189" t="n">
-        <v>92616</v>
+        <v>98360</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19811,37 +19815,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>691878</v>
+        <v>691699</v>
       </c>
       <c r="R189" t="n">
-        <v>7105889</v>
+        <v>7105908</v>
       </c>
       <c r="S189" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19885,48 +19889,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126868331</v>
+        <v>126868335</v>
       </c>
       <c r="B190" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19936,10 +19936,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>691780</v>
+        <v>691872</v>
       </c>
       <c r="R190" t="n">
-        <v>7105851</v>
+        <v>7105812</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19972,6 +19972,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>6 g:a fk.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20002,10 +20007,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126862203</v>
+        <v>126862182</v>
       </c>
       <c r="B191" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -20013,21 +20018,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20037,10 +20042,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>691745</v>
+        <v>691879</v>
       </c>
       <c r="R191" t="n">
-        <v>7105906</v>
+        <v>7105776</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20103,10 +20108,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126862182</v>
+        <v>126868331</v>
       </c>
       <c r="B192" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20114,21 +20119,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20138,10 +20143,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>691879</v>
+        <v>691780</v>
       </c>
       <c r="R192" t="n">
-        <v>7105776</v>
+        <v>7105851</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20188,12 +20193,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
@@ -20204,32 +20209,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126868335</v>
+        <v>126862203</v>
       </c>
       <c r="B193" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20239,10 +20244,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691872</v>
+        <v>691745</v>
       </c>
       <c r="R193" t="n">
-        <v>7105812</v>
+        <v>7105906</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20277,11 +20282,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>6 g:a fk.</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -20294,12 +20294,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20720,7 +20720,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126868478</v>
+        <v>126862180</v>
       </c>
       <c r="B198" t="n">
         <v>78773</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>692202</v>
+        <v>692178</v>
       </c>
       <c r="R198" t="n">
-        <v>7106954</v>
+        <v>7107022</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20805,12 +20805,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -20821,7 +20821,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126862180</v>
+        <v>126863150</v>
       </c>
       <c r="B199" t="n">
         <v>78773</v>
@@ -20856,10 +20856,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>692178</v>
+        <v>693008</v>
       </c>
       <c r="R199" t="n">
-        <v>7107022</v>
+        <v>7105846</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20906,12 +20906,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -20922,7 +20922,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126863150</v>
+        <v>126868478</v>
       </c>
       <c r="B200" t="n">
         <v>78773</v>
@@ -20957,10 +20957,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693008</v>
+        <v>692202</v>
       </c>
       <c r="R200" t="n">
-        <v>7105846</v>
+        <v>7106954</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21007,12 +21007,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -22130,10 +22130,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126868500</v>
+        <v>126862189</v>
       </c>
       <c r="B212" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -22141,21 +22141,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22165,10 +22165,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691846</v>
+        <v>692087</v>
       </c>
       <c r="R212" t="n">
-        <v>7107009</v>
+        <v>7107184</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22205,7 +22205,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>På hänsynssnitslad gran</t>
+          <t>Med apotecier</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22214,18 +22214,19 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
@@ -22236,10 +22237,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126862189</v>
+        <v>126868500</v>
       </c>
       <c r="B213" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -22247,21 +22248,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22271,10 +22272,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>692087</v>
+        <v>691846</v>
       </c>
       <c r="R213" t="n">
-        <v>7107184</v>
+        <v>7107009</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22311,7 +22312,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Med apotecier</t>
+          <t>På hänsynssnitslad gran</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22320,19 +22321,18 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
-      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -23847,32 +23847,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>126862198</v>
+        <v>126863151</v>
       </c>
       <c r="B229" t="n">
-        <v>80152</v>
+        <v>78773</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6463</v>
+        <v>228912</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23882,10 +23882,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>692221</v>
+        <v>692957</v>
       </c>
       <c r="R229" t="n">
-        <v>7106885</v>
+        <v>7105907</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23926,19 +23926,18 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -23949,56 +23948,48 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>126862174</v>
+        <v>126869138</v>
       </c>
       <c r="B230" t="n">
-        <v>57817</v>
+        <v>92616</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691869</v>
+        <v>692139</v>
       </c>
       <c r="R230" t="n">
-        <v>7106950</v>
+        <v>7106987</v>
       </c>
       <c r="S230" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -24042,12 +24033,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -24058,32 +24049,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>126863151</v>
+        <v>126862198</v>
       </c>
       <c r="B231" t="n">
-        <v>78773</v>
+        <v>80152</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>228912</v>
+        <v>6463</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24093,10 +24084,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>692957</v>
+        <v>692221</v>
       </c>
       <c r="R231" t="n">
-        <v>7105907</v>
+        <v>7106885</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24137,18 +24128,19 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -24159,48 +24151,56 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>126869138</v>
+        <v>126862174</v>
       </c>
       <c r="B232" t="n">
-        <v>92616</v>
+        <v>57817</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>692139</v>
+        <v>691869</v>
       </c>
       <c r="R232" t="n">
-        <v>7106987</v>
+        <v>7106950</v>
       </c>
       <c r="S232" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -24244,12 +24244,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -24761,32 +24761,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>126868501</v>
+        <v>126868517</v>
       </c>
       <c r="B238" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24796,10 +24796,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691785</v>
+        <v>691985</v>
       </c>
       <c r="R238" t="n">
-        <v>7107077</v>
+        <v>7107123</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24862,32 +24862,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>126868517</v>
+        <v>126868501</v>
       </c>
       <c r="B239" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24897,10 +24897,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691985</v>
+        <v>691785</v>
       </c>
       <c r="R239" t="n">
-        <v>7107123</v>
+        <v>7107077</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -6702,7 +6702,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126868320</v>
+        <v>126868316</v>
       </c>
       <c r="B61" t="n">
         <v>80117</v>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691833</v>
+        <v>691796</v>
       </c>
       <c r="R61" t="n">
-        <v>7106302</v>
+        <v>7106376</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt gammal grövre sälg.</t>
+          <t>Rikligt gammal sälg intill hyggeskant.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6808,32 +6808,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126868316</v>
+        <v>126867592</v>
       </c>
       <c r="B62" t="n">
-        <v>80117</v>
+        <v>79038</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6843,10 +6843,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691796</v>
+        <v>691747</v>
       </c>
       <c r="R62" t="n">
-        <v>7106376</v>
+        <v>7106703</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6881,11 +6881,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt gammal sälg intill hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6898,12 +6893,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6914,32 +6909,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126867592</v>
+        <v>126867623</v>
       </c>
       <c r="B63" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6949,10 +6944,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691747</v>
+        <v>691797</v>
       </c>
       <c r="R63" t="n">
-        <v>7106703</v>
+        <v>7106341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7015,7 +7010,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126867623</v>
+        <v>126862892</v>
       </c>
       <c r="B64" t="n">
         <v>79014</v>
@@ -7050,10 +7045,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>691797</v>
+        <v>691871</v>
       </c>
       <c r="R64" t="n">
-        <v>7106341</v>
+        <v>7106324</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7100,12 +7095,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7116,10 +7111,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126862892</v>
+        <v>126862176</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7127,34 +7122,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691871</v>
+        <v>692001</v>
       </c>
       <c r="R65" t="n">
-        <v>7106324</v>
+        <v>7106695</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7201,12 +7204,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7217,10 +7220,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126862176</v>
+        <v>126867634</v>
       </c>
       <c r="B66" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7228,42 +7231,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692001</v>
+        <v>691888</v>
       </c>
       <c r="R66" t="n">
-        <v>7106695</v>
+        <v>7106163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7310,12 +7305,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7326,32 +7321,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126865528</v>
+        <v>126868328</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7361,10 +7356,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691813</v>
+        <v>691816</v>
       </c>
       <c r="R67" t="n">
-        <v>7106581</v>
+        <v>7106552</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7399,6 +7394,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7411,12 +7411,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7427,32 +7427,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126868488</v>
+        <v>126868320</v>
       </c>
       <c r="B68" t="n">
-        <v>98443</v>
+        <v>80117</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691828</v>
+        <v>691833</v>
       </c>
       <c r="R68" t="n">
-        <v>7106415</v>
+        <v>7106302</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Blommande</t>
+          <t>Rikligt gammal grövre sälg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7517,12 +7517,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7533,32 +7533,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126867634</v>
+        <v>126865528</v>
       </c>
       <c r="B69" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691888</v>
+        <v>691813</v>
       </c>
       <c r="R69" t="n">
-        <v>7106163</v>
+        <v>7106581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7618,12 +7618,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7634,32 +7634,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126868328</v>
+        <v>126868488</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7669,10 +7669,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>691816</v>
+        <v>691828</v>
       </c>
       <c r="R70" t="n">
-        <v>7106552</v>
+        <v>7106415</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På äldre tall.</t>
+          <t>Blommande</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7724,12 +7724,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8245,32 +8245,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126867613</v>
+        <v>126862883</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>691720</v>
+        <v>691832</v>
       </c>
       <c r="R76" t="n">
-        <v>7106626</v>
+        <v>7106475</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,12 +8330,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8346,7 +8346,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126867636</v>
+        <v>126867625</v>
       </c>
       <c r="B77" t="n">
         <v>79014</v>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>691954</v>
+        <v>691792</v>
       </c>
       <c r="R77" t="n">
-        <v>7106198</v>
+        <v>7106323</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126867625</v>
+        <v>126868317</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8458,21 +8458,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>691792</v>
+        <v>691833</v>
       </c>
       <c r="R78" t="n">
-        <v>7106323</v>
+        <v>7106362</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8520,6 +8520,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På  "sälg låga".</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8532,12 +8537,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8548,7 +8553,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126868317</v>
+        <v>126865527</v>
       </c>
       <c r="B79" t="n">
         <v>80117</v>
@@ -8583,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>691833</v>
+        <v>691852</v>
       </c>
       <c r="R79" t="n">
-        <v>7106362</v>
+        <v>7106251</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8621,11 +8626,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På  "sälg låga".</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8638,12 +8638,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126865527</v>
+        <v>126868507</v>
       </c>
       <c r="B80" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>691852</v>
+        <v>691973</v>
       </c>
       <c r="R80" t="n">
-        <v>7106251</v>
+        <v>7106021</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8739,12 +8739,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8755,7 +8755,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126868507</v>
+        <v>126867613</v>
       </c>
       <c r="B81" t="n">
         <v>79014</v>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>691973</v>
+        <v>691720</v>
       </c>
       <c r="R81" t="n">
-        <v>7106021</v>
+        <v>7106626</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,12 +8840,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126862883</v>
+        <v>126867636</v>
       </c>
       <c r="B82" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>691832</v>
+        <v>691954</v>
       </c>
       <c r="R82" t="n">
-        <v>7106475</v>
+        <v>7106198</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8941,12 +8941,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8957,32 +8957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126867627</v>
+        <v>126865530</v>
       </c>
       <c r="B83" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>691826</v>
+        <v>691847</v>
       </c>
       <c r="R83" t="n">
-        <v>7106291</v>
+        <v>7106512</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9042,12 +9042,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9058,7 +9058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126868492</v>
+        <v>126867627</v>
       </c>
       <c r="B84" t="n">
         <v>79014</v>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>692005</v>
+        <v>691826</v>
       </c>
       <c r="R84" t="n">
-        <v>7106694</v>
+        <v>7106291</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9143,12 +9143,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9159,53 +9159,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126862859</v>
+        <v>126868492</v>
       </c>
       <c r="B85" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>691967</v>
+        <v>692005</v>
       </c>
       <c r="R85" t="n">
-        <v>7106021</v>
+        <v>7106694</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9240,11 +9232,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Solgrop och tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9257,12 +9244,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9273,45 +9260,53 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126865530</v>
+        <v>126862859</v>
       </c>
       <c r="B86" t="n">
-        <v>98443</v>
+        <v>56849</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>691847</v>
+        <v>691967</v>
       </c>
       <c r="R86" t="n">
-        <v>7106512</v>
+        <v>7106021</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9346,6 +9341,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Solgrop och tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9358,12 +9358,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -12117,7 +12117,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126867632</v>
+        <v>126868493</v>
       </c>
       <c r="B114" t="n">
         <v>79014</v>
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>691815</v>
+        <v>691997</v>
       </c>
       <c r="R114" t="n">
-        <v>7106269</v>
+        <v>7106738</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,12 +12202,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12218,7 +12218,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126868493</v>
+        <v>126867614</v>
       </c>
       <c r="B115" t="n">
         <v>79014</v>
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>691997</v>
+        <v>691757</v>
       </c>
       <c r="R115" t="n">
-        <v>7106738</v>
+        <v>7106584</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12303,12 +12303,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12319,27 +12319,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126867614</v>
+        <v>126856407</v>
       </c>
       <c r="B116" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>691757</v>
+        <v>692211</v>
       </c>
       <c r="R116" t="n">
-        <v>7106584</v>
+        <v>7106863</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12404,48 +12404,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126856407</v>
+        <v>126868325</v>
       </c>
       <c r="B117" t="n">
-        <v>80152</v>
+        <v>98443</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12455,10 +12451,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>692211</v>
+        <v>691824</v>
       </c>
       <c r="R117" t="n">
-        <v>7106863</v>
+        <v>7106438</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12493,6 +12489,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>1 blomma.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -12505,22 +12506,26 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126862177</v>
+        <v>126867632</v>
       </c>
       <c r="B118" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12528,42 +12533,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>692018</v>
+        <v>691815</v>
       </c>
       <c r="R118" t="n">
-        <v>7106688</v>
+        <v>7106269</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12610,12 +12607,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12626,45 +12623,53 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126868325</v>
+        <v>126862177</v>
       </c>
       <c r="B119" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>691824</v>
+        <v>692018</v>
       </c>
       <c r="R119" t="n">
-        <v>7106438</v>
+        <v>7106688</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12699,11 +12704,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1 blomma.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12716,12 +12716,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -17545,32 +17545,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126868470</v>
+        <v>126862465</v>
       </c>
       <c r="B167" t="n">
-        <v>79632</v>
+        <v>98464</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17580,10 +17580,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691906</v>
+        <v>691913</v>
       </c>
       <c r="R167" t="n">
-        <v>7105789</v>
+        <v>7105810</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17618,6 +17618,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>&gt;10 ex</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -17630,61 +17635,69 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126862170</v>
+        <v>126862862</v>
       </c>
       <c r="B168" t="n">
-        <v>79632</v>
+        <v>56849</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691866</v>
+        <v>691772</v>
       </c>
       <c r="R168" t="n">
-        <v>7105795</v>
+        <v>7105816</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17719,6 +17732,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Flygfärdig kyckling med höna</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17731,12 +17749,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17747,57 +17765,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126862862</v>
+        <v>126868470</v>
       </c>
       <c r="B169" t="n">
-        <v>56849</v>
+        <v>79632</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691772</v>
+        <v>691906</v>
       </c>
       <c r="R169" t="n">
-        <v>7105816</v>
+        <v>7105789</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17832,11 +17838,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Flygfärdig kyckling med höna</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17849,12 +17850,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17865,32 +17866,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126862465</v>
+        <v>126862170</v>
       </c>
       <c r="B170" t="n">
-        <v>98464</v>
+        <v>79632</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17900,10 +17901,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691913</v>
+        <v>691866</v>
       </c>
       <c r="R170" t="n">
-        <v>7105810</v>
+        <v>7105795</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17938,11 +17939,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>&gt;10 ex</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -17955,22 +17951,26 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126867644</v>
+        <v>126868315</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17978,21 +17978,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691975</v>
+        <v>691875</v>
       </c>
       <c r="R171" t="n">
-        <v>7105718</v>
+        <v>7105775</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18052,12 +18052,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18068,10 +18068,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126868315</v>
+        <v>126867644</v>
       </c>
       <c r="B172" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18079,21 +18079,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691875</v>
+        <v>691975</v>
       </c>
       <c r="R172" t="n">
-        <v>7105775</v>
+        <v>7105718</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18153,12 +18153,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -19602,48 +19602,48 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126869139</v>
+        <v>126867672</v>
       </c>
       <c r="B187" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>691878</v>
+        <v>691693</v>
       </c>
       <c r="R187" t="n">
-        <v>7105889</v>
+        <v>7105912</v>
       </c>
       <c r="S187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19687,12 +19687,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -19703,32 +19703,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126867672</v>
+        <v>126862473</v>
       </c>
       <c r="B188" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19738,10 +19738,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>691693</v>
+        <v>691699</v>
       </c>
       <c r="R188" t="n">
-        <v>7105912</v>
+        <v>7105908</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19788,26 +19788,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY188" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>126862473</v>
+        <v>126869139</v>
       </c>
       <c r="B189" t="n">
-        <v>98360</v>
+        <v>92616</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -19815,37 +19811,37 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>691699</v>
+        <v>691878</v>
       </c>
       <c r="R189" t="n">
-        <v>7105908</v>
+        <v>7105889</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -19889,15 +19885,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr"/>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -24761,32 +24761,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>126868517</v>
+        <v>126868501</v>
       </c>
       <c r="B238" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24796,10 +24796,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691985</v>
+        <v>691785</v>
       </c>
       <c r="R238" t="n">
-        <v>7107123</v>
+        <v>7107077</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24862,32 +24862,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>126868501</v>
+        <v>126868517</v>
       </c>
       <c r="B239" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24897,10 +24897,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691785</v>
+        <v>691985</v>
       </c>
       <c r="R239" t="n">
-        <v>7107077</v>
+        <v>7107123</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -1808,10 +1808,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126851931</v>
+        <v>126867612</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,21 +1819,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691748</v>
+        <v>691700</v>
       </c>
       <c r="R13" t="n">
-        <v>7105951</v>
+        <v>7106739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,22 +1893,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126862178</v>
+        <v>126851931</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,42 +1920,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691990</v>
+        <v>691748</v>
       </c>
       <c r="R14" t="n">
-        <v>7106753</v>
+        <v>7105951</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,26 +1994,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126867612</v>
+        <v>126862178</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,34 +2017,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691700</v>
+        <v>691990</v>
       </c>
       <c r="R15" t="n">
-        <v>7106739</v>
+        <v>7106753</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2099,12 +2099,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2317,32 +2317,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867678</v>
+        <v>126867621</v>
       </c>
       <c r="B18" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691823</v>
+        <v>691806</v>
       </c>
       <c r="R18" t="n">
-        <v>7106209</v>
+        <v>7106380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,32 +2418,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126862867</v>
+        <v>126867678</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691830</v>
+        <v>691823</v>
       </c>
       <c r="R19" t="n">
-        <v>7106333</v>
+        <v>7106209</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,12 +2503,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2519,7 +2519,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126868486</v>
+        <v>126862867</v>
       </c>
       <c r="B20" t="n">
         <v>80121</v>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691983</v>
+        <v>691830</v>
       </c>
       <c r="R20" t="n">
-        <v>7106781</v>
+        <v>7106333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,12 +2604,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2620,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126852151</v>
+        <v>126868486</v>
       </c>
       <c r="B21" t="n">
-        <v>79104</v>
+        <v>80121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6450</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691715</v>
+        <v>691983</v>
       </c>
       <c r="R21" t="n">
-        <v>7105958</v>
+        <v>7106781</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,44 +2705,48 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126862877</v>
+        <v>126852151</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>79104</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2752,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691827</v>
+        <v>691715</v>
       </c>
       <c r="R22" t="n">
-        <v>7106338</v>
+        <v>7105958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,64 +2806,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126868322</v>
+        <v>126869129</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>57765</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691828</v>
+        <v>692001</v>
       </c>
       <c r="R23" t="n">
-        <v>7106429</v>
+        <v>7106677</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2889,11 +2897,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En blomma + 7-8 plantor.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2908,12 +2911,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2924,32 +2927,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126867621</v>
+        <v>126862877</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2962,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691806</v>
+        <v>691827</v>
       </c>
       <c r="R24" t="n">
-        <v>7106380</v>
+        <v>7106338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,12 +3012,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3025,56 +3028,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126869129</v>
+        <v>126868322</v>
       </c>
       <c r="B25" t="n">
-        <v>57765</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>692001</v>
+        <v>691828</v>
       </c>
       <c r="R25" t="n">
-        <v>7106677</v>
+        <v>7106429</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3104,6 +3099,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>En blomma + 7-8 plantor.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3118,12 +3118,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3134,10 +3134,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126867630</v>
+        <v>126868483</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691829</v>
+        <v>691825</v>
       </c>
       <c r="R26" t="n">
-        <v>7106294</v>
+        <v>7106330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,6 +3207,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3219,12 +3224,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3235,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126868327</v>
+        <v>126859325</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3246,21 +3251,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3270,10 +3275,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691816</v>
+        <v>691835</v>
       </c>
       <c r="R27" t="n">
-        <v>7106553</v>
+        <v>7106328</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,11 +3313,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3325,61 +3325,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126862881</v>
+        <v>126868442</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691808</v>
+        <v>691999</v>
       </c>
       <c r="R28" t="n">
-        <v>7106575</v>
+        <v>7106730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126868483</v>
+        <v>126867630</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691825</v>
+        <v>691829</v>
       </c>
       <c r="R29" t="n">
-        <v>7106330</v>
+        <v>7106294</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,11 +3515,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3532,12 +3527,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3548,10 +3543,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126859325</v>
+        <v>126868327</v>
       </c>
       <c r="B30" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3559,21 +3554,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3583,10 +3578,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691835</v>
+        <v>691816</v>
       </c>
       <c r="R30" t="n">
-        <v>7106328</v>
+        <v>7106553</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3621,6 +3616,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3633,61 +3633,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126868442</v>
+        <v>126862881</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691999</v>
+        <v>691808</v>
       </c>
       <c r="R31" t="n">
-        <v>7106730</v>
+        <v>7106575</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,12 +3734,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3750,32 +3750,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126867640</v>
+        <v>126867684</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691978</v>
+        <v>691963</v>
       </c>
       <c r="R32" t="n">
-        <v>7106086</v>
+        <v>7106099</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3851,32 +3851,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126867684</v>
+        <v>126867640</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691963</v>
+        <v>691978</v>
       </c>
       <c r="R33" t="n">
-        <v>7106099</v>
+        <v>7106086</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -6702,32 +6702,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126867634</v>
+        <v>126867592</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691888</v>
+        <v>691747</v>
       </c>
       <c r="R61" t="n">
-        <v>7106163</v>
+        <v>7106703</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126867623</v>
+        <v>126862892</v>
       </c>
       <c r="B62" t="n">
         <v>79018</v>
@@ -6838,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691797</v>
+        <v>691871</v>
       </c>
       <c r="R62" t="n">
-        <v>7106341</v>
+        <v>7106324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6888,12 +6888,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6904,10 +6904,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126868328</v>
+        <v>126862176</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6915,34 +6915,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691816</v>
+        <v>692001</v>
       </c>
       <c r="R63" t="n">
-        <v>7106552</v>
+        <v>7106695</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6977,11 +6985,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6994,12 +6997,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7010,10 +7013,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126868320</v>
+        <v>126867634</v>
       </c>
       <c r="B64" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7021,21 +7024,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7045,10 +7048,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>691833</v>
+        <v>691888</v>
       </c>
       <c r="R64" t="n">
-        <v>7106302</v>
+        <v>7106163</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,11 +7086,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt gammal grövre sälg.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7100,12 +7098,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7116,10 +7114,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126868316</v>
+        <v>126867623</v>
       </c>
       <c r="B65" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7127,21 +7125,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7151,10 +7149,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691796</v>
+        <v>691797</v>
       </c>
       <c r="R65" t="n">
-        <v>7106376</v>
+        <v>7106341</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7189,11 +7187,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt gammal sälg intill hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7206,12 +7199,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7222,32 +7215,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126867592</v>
+        <v>126868328</v>
       </c>
       <c r="B66" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7257,10 +7250,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691747</v>
+        <v>691816</v>
       </c>
       <c r="R66" t="n">
-        <v>7106703</v>
+        <v>7106552</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7295,6 +7288,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7307,12 +7305,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7323,10 +7321,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126862892</v>
+        <v>126868320</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7334,21 +7332,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7358,10 +7356,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691871</v>
+        <v>691833</v>
       </c>
       <c r="R67" t="n">
-        <v>7106324</v>
+        <v>7106302</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7396,6 +7394,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt gammal grövre sälg.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7408,12 +7411,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7424,10 +7427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126862176</v>
+        <v>126868316</v>
       </c>
       <c r="B68" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7435,42 +7438,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>692001</v>
+        <v>691796</v>
       </c>
       <c r="R68" t="n">
-        <v>7106695</v>
+        <v>7106376</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7505,6 +7500,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt gammal sälg intill hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7517,12 +7517,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7740,32 +7740,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126862873</v>
+        <v>126862874</v>
       </c>
       <c r="B71" t="n">
-        <v>78776</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>691721</v>
+        <v>691824</v>
       </c>
       <c r="R71" t="n">
-        <v>7105960</v>
+        <v>7106450</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7841,10 +7841,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126862855</v>
+        <v>126862873</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7852,21 +7852,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7942,10 +7942,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126867617</v>
+        <v>126862855</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7953,21 +7953,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>691814</v>
+        <v>691721</v>
       </c>
       <c r="R73" t="n">
-        <v>7106474</v>
+        <v>7105960</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8027,12 +8027,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -8043,32 +8043,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126862874</v>
+        <v>126867617</v>
       </c>
       <c r="B74" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>691824</v>
+        <v>691814</v>
       </c>
       <c r="R74" t="n">
-        <v>7106450</v>
+        <v>7106474</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8128,12 +8128,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -9374,10 +9374,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126862864</v>
+        <v>126867618</v>
       </c>
       <c r="B87" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>691833</v>
+        <v>691826</v>
       </c>
       <c r="R87" t="n">
-        <v>7106331</v>
+        <v>7106372</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9447,11 +9447,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Bohål i asp. 7-9 cm i diameter</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9464,12 +9459,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9480,45 +9475,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126867618</v>
+        <v>126865721</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>691826</v>
+        <v>691719</v>
       </c>
       <c r="R88" t="n">
-        <v>7106372</v>
+        <v>7105959</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9559,18 +9557,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9581,48 +9580,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126865721</v>
+        <v>126868498</v>
       </c>
       <c r="B89" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>691719</v>
+        <v>691899</v>
       </c>
       <c r="R89" t="n">
-        <v>7105959</v>
+        <v>7106892</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9657,25 +9653,29 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Mycket på gammal gran</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9787,10 +9787,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126868498</v>
+        <v>126862864</v>
       </c>
       <c r="B91" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9798,21 +9798,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>691899</v>
+        <v>691833</v>
       </c>
       <c r="R91" t="n">
-        <v>7106892</v>
+        <v>7106331</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Mycket på gammal gran</t>
+          <t>Bohål i asp. 7-9 cm i diameter</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9877,12 +9877,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11515,10 +11515,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126867638</v>
+        <v>126867610</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11526,21 +11526,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11550,10 +11550,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>691977</v>
+        <v>691783</v>
       </c>
       <c r="R108" t="n">
-        <v>7106091</v>
+        <v>7106563</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126867610</v>
+        <v>126852645</v>
       </c>
       <c r="B109" t="n">
         <v>78776</v>
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>691783</v>
+        <v>691715</v>
       </c>
       <c r="R109" t="n">
-        <v>7106563</v>
+        <v>7105958</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11701,48 +11701,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126852645</v>
+        <v>126868314</v>
       </c>
       <c r="B110" t="n">
-        <v>78776</v>
+        <v>97331</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11752,10 +11748,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>691715</v>
+        <v>691991</v>
       </c>
       <c r="R110" t="n">
-        <v>7105958</v>
+        <v>7106099</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11802,60 +11798,64 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126868314</v>
+        <v>126869123</v>
       </c>
       <c r="B111" t="n">
-        <v>97331</v>
+        <v>79050</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>691991</v>
+        <v>691917</v>
       </c>
       <c r="R111" t="n">
-        <v>7106099</v>
+        <v>7106857</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11899,12 +11899,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -11915,7 +11915,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126862890</v>
+        <v>126867638</v>
       </c>
       <c r="B112" t="n">
         <v>79018</v>
@@ -11950,10 +11950,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>691859</v>
+        <v>691977</v>
       </c>
       <c r="R112" t="n">
-        <v>7106523</v>
+        <v>7106091</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12000,12 +12000,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -12016,10 +12016,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126869123</v>
+        <v>126862890</v>
       </c>
       <c r="B113" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12027,37 +12027,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>691917</v>
+        <v>691859</v>
       </c>
       <c r="R113" t="n">
-        <v>7106857</v>
+        <v>7106523</v>
       </c>
       <c r="S113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12101,12 +12101,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12732,32 +12732,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126868473</v>
+        <v>126868494</v>
       </c>
       <c r="B120" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>691977</v>
+        <v>691985</v>
       </c>
       <c r="R120" t="n">
-        <v>7106779</v>
+        <v>7106752</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12811,7 +12811,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12834,32 +12833,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126868318</v>
+        <v>126868473</v>
       </c>
       <c r="B121" t="n">
-        <v>80121</v>
+        <v>80150</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12869,10 +12868,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>691844</v>
+        <v>691977</v>
       </c>
       <c r="R121" t="n">
-        <v>7106329</v>
+        <v>7106779</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12907,29 +12906,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12940,10 +12935,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126868464</v>
+        <v>126868318</v>
       </c>
       <c r="B122" t="n">
-        <v>75142</v>
+        <v>80121</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12951,21 +12946,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12975,10 +12970,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>692154</v>
+        <v>691844</v>
       </c>
       <c r="R122" t="n">
-        <v>7106591</v>
+        <v>7106329</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13013,6 +13008,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -13025,12 +13025,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -13041,10 +13041,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126868497</v>
+        <v>126868464</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13052,21 +13052,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13076,10 +13076,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>691928</v>
+        <v>692154</v>
       </c>
       <c r="R123" t="n">
-        <v>7106864</v>
+        <v>7106591</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13112,11 +13112,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13147,32 +13142,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126867594</v>
+        <v>126868497</v>
       </c>
       <c r="B124" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13182,10 +13177,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691827</v>
+        <v>691928</v>
       </c>
       <c r="R124" t="n">
-        <v>7106280</v>
+        <v>7106864</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13220,6 +13215,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På gammal grov gran</t>
+        </is>
+      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -13232,12 +13232,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
@@ -13248,32 +13248,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126862886</v>
+        <v>126867594</v>
       </c>
       <c r="B125" t="n">
-        <v>98447</v>
+        <v>79042</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13283,10 +13283,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>691817</v>
+        <v>691827</v>
       </c>
       <c r="R125" t="n">
-        <v>7106463</v>
+        <v>7106280</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13333,12 +13333,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13349,7 +13349,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126862191</v>
+        <v>126862886</v>
       </c>
       <c r="B126" t="n">
         <v>98447</v>
@@ -13378,20 +13378,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>691819</v>
+        <v>691817</v>
       </c>
       <c r="R126" t="n">
-        <v>7106338</v>
+        <v>7106463</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13432,19 +13428,18 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13455,7 +13450,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126868326</v>
+        <v>126862191</v>
       </c>
       <c r="B127" t="n">
         <v>98447</v>
@@ -13484,16 +13479,20 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691820</v>
+        <v>691819</v>
       </c>
       <c r="R127" t="n">
-        <v>7106411</v>
+        <v>7106338</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13528,29 +13527,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13561,32 +13556,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126868494</v>
+        <v>126868326</v>
       </c>
       <c r="B128" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13596,10 +13591,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>691985</v>
+        <v>691820</v>
       </c>
       <c r="R128" t="n">
-        <v>7106752</v>
+        <v>7106411</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13634,6 +13629,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -13646,12 +13646,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13864,32 +13864,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126867596</v>
+        <v>126862204</v>
       </c>
       <c r="B131" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13899,10 +13899,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>691792</v>
+        <v>691923</v>
       </c>
       <c r="R131" t="n">
-        <v>7105766</v>
+        <v>7105710</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13949,12 +13949,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13965,32 +13965,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126862204</v>
+        <v>126867596</v>
       </c>
       <c r="B132" t="n">
-        <v>79018</v>
+        <v>79042</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14000,10 +14000,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>691923</v>
+        <v>691792</v>
       </c>
       <c r="R132" t="n">
-        <v>7105710</v>
+        <v>7105766</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14050,12 +14050,12 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -14066,32 +14066,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126868338</v>
+        <v>126867655</v>
       </c>
       <c r="B133" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14101,10 +14101,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691750</v>
+        <v>691840</v>
       </c>
       <c r="R133" t="n">
-        <v>7105871</v>
+        <v>7105751</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14139,11 +14139,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Tre g:a fk.</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14156,12 +14151,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14172,10 +14167,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126862860</v>
+        <v>126868338</v>
       </c>
       <c r="B134" t="n">
-        <v>56853</v>
+        <v>92620</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14183,50 +14178,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691767</v>
+        <v>691750</v>
       </c>
       <c r="R134" t="n">
-        <v>7105824</v>
+        <v>7105871</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14263,7 +14242,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Höna med kyckling</t>
+          <t>Tre g:a fk.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14278,12 +14257,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14294,45 +14273,61 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126867655</v>
+        <v>126862860</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691840</v>
+        <v>691767</v>
       </c>
       <c r="R135" t="n">
-        <v>7105751</v>
+        <v>7105824</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14367,6 +14362,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Höna med kyckling</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -14379,12 +14379,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14395,10 +14395,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126867654</v>
+        <v>126869124</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14406,37 +14406,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691851</v>
+        <v>691841</v>
       </c>
       <c r="R136" t="n">
-        <v>7105739</v>
+        <v>7105771</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14474,18 +14474,19 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14496,7 +14497,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126867668</v>
+        <v>126867654</v>
       </c>
       <c r="B137" t="n">
         <v>79018</v>
@@ -14531,10 +14532,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691702</v>
+        <v>691851</v>
       </c>
       <c r="R137" t="n">
-        <v>7105912</v>
+        <v>7105739</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14597,32 +14598,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126868475</v>
+        <v>126867668</v>
       </c>
       <c r="B138" t="n">
-        <v>58492</v>
+        <v>79018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>208245</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14632,10 +14633,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691770</v>
+        <v>691702</v>
       </c>
       <c r="R138" t="n">
-        <v>7105834</v>
+        <v>7105912</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14682,12 +14683,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14698,32 +14699,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126863145</v>
+        <v>126868475</v>
       </c>
       <c r="B139" t="n">
-        <v>79607</v>
+        <v>58492</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>208245</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14733,10 +14734,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691819</v>
+        <v>691770</v>
       </c>
       <c r="R139" t="n">
-        <v>7105865</v>
+        <v>7105834</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14783,12 +14784,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14799,10 +14800,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126869124</v>
+        <v>126863145</v>
       </c>
       <c r="B140" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14810,37 +14811,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691841</v>
+        <v>691819</v>
       </c>
       <c r="R140" t="n">
-        <v>7105771</v>
+        <v>7105865</v>
       </c>
       <c r="S140" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14878,19 +14879,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15709,10 +15709,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126862471</v>
+        <v>126868301</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15720,21 +15720,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>691883</v>
+        <v>691717</v>
       </c>
       <c r="R149" t="n">
-        <v>7105746</v>
+        <v>7105891</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15794,22 +15794,26 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126868301</v>
+        <v>126867670</v>
       </c>
       <c r="B150" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15817,21 +15821,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15841,10 +15845,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>691717</v>
+        <v>691697</v>
       </c>
       <c r="R150" t="n">
-        <v>7105891</v>
+        <v>7105917</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15891,12 +15895,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15907,7 +15911,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126867670</v>
+        <v>126867659</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -15942,10 +15946,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691697</v>
+        <v>691800</v>
       </c>
       <c r="R151" t="n">
-        <v>7105917</v>
+        <v>7105765</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16008,10 +16012,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126867659</v>
+        <v>126862205</v>
       </c>
       <c r="B152" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16019,21 +16023,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16043,10 +16047,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691800</v>
+        <v>691964</v>
       </c>
       <c r="R152" t="n">
-        <v>7105765</v>
+        <v>7105748</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16093,12 +16097,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16109,10 +16113,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126862205</v>
+        <v>126862471</v>
       </c>
       <c r="B153" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16120,21 +16124,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16144,10 +16148,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691964</v>
+        <v>691883</v>
       </c>
       <c r="R153" t="n">
-        <v>7105748</v>
+        <v>7105746</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16194,26 +16198,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126868305</v>
+        <v>126868476</v>
       </c>
       <c r="B154" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16221,21 +16221,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16245,10 +16245,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691870</v>
+        <v>691786</v>
       </c>
       <c r="R154" t="n">
-        <v>7105761</v>
+        <v>7105813</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16295,12 +16295,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16311,10 +16311,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126868476</v>
+        <v>126868305</v>
       </c>
       <c r="B155" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16322,21 +16322,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16346,10 +16346,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691786</v>
+        <v>691870</v>
       </c>
       <c r="R155" t="n">
-        <v>7105813</v>
+        <v>7105761</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16396,12 +16396,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -18169,10 +18169,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126863153</v>
+        <v>126868509</v>
       </c>
       <c r="B173" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18180,21 +18180,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691843</v>
+        <v>691892</v>
       </c>
       <c r="R173" t="n">
-        <v>7105861</v>
+        <v>7105763</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18242,6 +18242,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ganska mycket på tallarna</t>
+        </is>
+      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18254,12 +18259,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18270,7 +18275,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126868509</v>
+        <v>126867642</v>
       </c>
       <c r="B174" t="n">
         <v>79018</v>
@@ -18305,10 +18310,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691892</v>
+        <v>691963</v>
       </c>
       <c r="R174" t="n">
-        <v>7105763</v>
+        <v>7105736</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18343,11 +18348,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Ganska mycket på tallarna</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18360,12 +18360,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18376,10 +18376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126867642</v>
+        <v>126869131</v>
       </c>
       <c r="B175" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18387,37 +18387,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691963</v>
+        <v>691873</v>
       </c>
       <c r="R175" t="n">
-        <v>7105736</v>
+        <v>7105745</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18461,12 +18461,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18477,10 +18477,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126869131</v>
+        <v>126863153</v>
       </c>
       <c r="B176" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18488,37 +18488,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691873</v>
+        <v>691843</v>
       </c>
       <c r="R176" t="n">
-        <v>7105745</v>
+        <v>7105861</v>
       </c>
       <c r="S176" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18562,12 +18562,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -19901,7 +19901,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126868331</v>
+        <v>126862203</v>
       </c>
       <c r="B190" t="n">
         <v>79018</v>
@@ -19936,10 +19936,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>691780</v>
+        <v>691745</v>
       </c>
       <c r="R190" t="n">
-        <v>7105851</v>
+        <v>7105906</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19986,12 +19986,12 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
@@ -20002,32 +20002,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126862203</v>
+        <v>126868335</v>
       </c>
       <c r="B191" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20037,10 +20037,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>691745</v>
+        <v>691872</v>
       </c>
       <c r="R191" t="n">
-        <v>7105906</v>
+        <v>7105812</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20075,6 +20075,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>6 g:a fk.</t>
+        </is>
+      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -20087,12 +20092,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
@@ -20103,32 +20108,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126868335</v>
+        <v>126868331</v>
       </c>
       <c r="B192" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20138,10 +20143,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>691872</v>
+        <v>691780</v>
       </c>
       <c r="R192" t="n">
-        <v>7105812</v>
+        <v>7105851</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20174,11 +20179,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>6 g:a fk.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21330,32 +21330,32 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126863159</v>
+        <v>126863164</v>
       </c>
       <c r="B204" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21365,10 +21365,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>692648</v>
+        <v>692997</v>
       </c>
       <c r="R204" t="n">
-        <v>7105942</v>
+        <v>7105875</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21431,7 +21431,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126863164</v>
+        <v>126862474</v>
       </c>
       <c r="B205" t="n">
         <v>92620</v>
@@ -21466,10 +21466,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>692997</v>
+        <v>692634</v>
       </c>
       <c r="R205" t="n">
-        <v>7105875</v>
+        <v>7105939</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21516,26 +21516,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY205" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126862474</v>
+        <v>126855997</v>
       </c>
       <c r="B206" t="n">
-        <v>92620</v>
+        <v>80025</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -21543,21 +21539,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21567,10 +21563,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>692634</v>
+        <v>692255</v>
       </c>
       <c r="R206" t="n">
-        <v>7105939</v>
+        <v>7106775</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21617,44 +21613,44 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126855997</v>
+        <v>126863159</v>
       </c>
       <c r="B207" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21664,10 +21660,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>692255</v>
+        <v>692648</v>
       </c>
       <c r="R207" t="n">
-        <v>7106775</v>
+        <v>7105942</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21714,15 +21710,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY207" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -996,48 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126867049</v>
+        <v>126868496</v>
       </c>
       <c r="B5" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691961</v>
+        <v>691941</v>
       </c>
       <c r="R5" t="n">
-        <v>7106020</v>
+        <v>7106860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1075,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1101,45 +1097,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126865523</v>
+        <v>126867049</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691797</v>
+        <v>691961</v>
       </c>
       <c r="R6" t="n">
-        <v>7106375</v>
+        <v>7106020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,18 +1179,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1202,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868503</v>
+        <v>126865523</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1213,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692149</v>
+        <v>691797</v>
       </c>
       <c r="R7" t="n">
-        <v>7106588</v>
+        <v>7106375</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,12 +1287,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1303,32 +1303,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126868496</v>
+        <v>126862876</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691941</v>
+        <v>691847</v>
       </c>
       <c r="R8" t="n">
-        <v>7106860</v>
+        <v>7106392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,12 +1388,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126862876</v>
+        <v>126862884</v>
       </c>
       <c r="B9" t="n">
         <v>98447</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691847</v>
+        <v>691817</v>
       </c>
       <c r="R9" t="n">
-        <v>7106392</v>
+        <v>7106456</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,32 +1505,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126862884</v>
+        <v>126867602</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691817</v>
+        <v>691670</v>
       </c>
       <c r="R10" t="n">
-        <v>7106456</v>
+        <v>7106776</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1590,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126867602</v>
+        <v>126868503</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,21 +1617,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691670</v>
+        <v>692149</v>
       </c>
       <c r="R11" t="n">
-        <v>7106776</v>
+        <v>7106588</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,12 +1691,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2216,48 +2216,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126862196</v>
+        <v>126869129</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>57765</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691978</v>
+        <v>692001</v>
       </c>
       <c r="R17" t="n">
-        <v>7106752</v>
+        <v>7106677</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2301,12 +2309,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2317,32 +2325,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126867621</v>
+        <v>126862877</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2352,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691806</v>
+        <v>691827</v>
       </c>
       <c r="R18" t="n">
-        <v>7106380</v>
+        <v>7106338</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,12 +2410,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2418,32 +2426,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126867678</v>
+        <v>126868322</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>98447</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2453,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691823</v>
+        <v>691828</v>
       </c>
       <c r="R19" t="n">
-        <v>7106209</v>
+        <v>7106429</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,6 +2499,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En blomma + 7-8 plantor.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2503,12 +2516,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2519,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126862867</v>
+        <v>126862196</v>
       </c>
       <c r="B20" t="n">
-        <v>80121</v>
+        <v>91326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,21 +2543,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2554,10 +2567,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691830</v>
+        <v>691978</v>
       </c>
       <c r="R20" t="n">
-        <v>7106333</v>
+        <v>7106752</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,12 +2617,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2620,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126868486</v>
+        <v>126867621</v>
       </c>
       <c r="B21" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,21 +2644,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2668,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691983</v>
+        <v>691806</v>
       </c>
       <c r="R21" t="n">
-        <v>7106781</v>
+        <v>7106380</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,12 +2718,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2721,10 +2734,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126852151</v>
+        <v>126867678</v>
       </c>
       <c r="B22" t="n">
-        <v>79104</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2732,21 +2745,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2769,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691715</v>
+        <v>691823</v>
       </c>
       <c r="R22" t="n">
-        <v>7105958</v>
+        <v>7106209</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2806,68 +2819,64 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126869129</v>
+        <v>126862867</v>
       </c>
       <c r="B23" t="n">
-        <v>57765</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>692001</v>
+        <v>691830</v>
       </c>
       <c r="R23" t="n">
-        <v>7106677</v>
+        <v>7106333</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2911,12 +2920,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2927,32 +2936,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126862877</v>
+        <v>126868486</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2962,10 +2971,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691827</v>
+        <v>691983</v>
       </c>
       <c r="R24" t="n">
-        <v>7106338</v>
+        <v>7106781</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3012,12 +3021,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3028,32 +3037,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126868322</v>
+        <v>126852151</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>79104</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691828</v>
+        <v>691715</v>
       </c>
       <c r="R25" t="n">
-        <v>7106429</v>
+        <v>7105958</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,11 +3110,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>En blomma + 7-8 plantor.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3118,26 +3122,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126868483</v>
+        <v>126867630</v>
       </c>
       <c r="B26" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691825</v>
+        <v>691829</v>
       </c>
       <c r="R26" t="n">
-        <v>7106330</v>
+        <v>7106294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,11 +3207,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3224,12 +3219,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3240,10 +3235,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126859325</v>
+        <v>126868327</v>
       </c>
       <c r="B27" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3251,21 +3246,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3270,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691835</v>
+        <v>691816</v>
       </c>
       <c r="R27" t="n">
-        <v>7106328</v>
+        <v>7106553</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,6 +3308,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3325,61 +3325,61 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126868442</v>
+        <v>126862881</v>
       </c>
       <c r="B28" t="n">
-        <v>57661</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691999</v>
+        <v>691808</v>
       </c>
       <c r="R28" t="n">
-        <v>7106730</v>
+        <v>7106575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3426,12 +3426,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3442,10 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126867630</v>
+        <v>126868483</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,21 +3453,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3477,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691829</v>
+        <v>691825</v>
       </c>
       <c r="R29" t="n">
-        <v>7106294</v>
+        <v>7106330</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,6 +3515,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3527,12 +3532,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3543,10 +3548,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126868327</v>
+        <v>126859325</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3554,21 +3559,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3578,10 +3583,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691816</v>
+        <v>691835</v>
       </c>
       <c r="R30" t="n">
-        <v>7106553</v>
+        <v>7106328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,11 +3621,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3633,61 +3633,61 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126862881</v>
+        <v>126868442</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691808</v>
+        <v>691999</v>
       </c>
       <c r="R31" t="n">
-        <v>7106575</v>
+        <v>7106730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3734,12 +3734,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -4255,10 +4255,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126867616</v>
+        <v>126868466</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691811</v>
+        <v>692151</v>
       </c>
       <c r="R37" t="n">
-        <v>7106492</v>
+        <v>7106586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4340,12 +4340,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4356,32 +4356,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126868484</v>
+        <v>126862895</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>91904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691825</v>
+        <v>691850</v>
       </c>
       <c r="R38" t="n">
-        <v>7106372</v>
+        <v>7106258</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4429,11 +4429,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4446,12 +4441,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4462,10 +4457,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126867603</v>
+        <v>126867616</v>
       </c>
       <c r="B39" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,21 +4468,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4497,10 +4492,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691608</v>
+        <v>691811</v>
       </c>
       <c r="R39" t="n">
-        <v>7106686</v>
+        <v>7106492</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4563,32 +4558,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126865524</v>
+        <v>126868311</v>
       </c>
       <c r="B40" t="n">
-        <v>80121</v>
+        <v>98468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4598,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691833</v>
+        <v>691808</v>
       </c>
       <c r="R40" t="n">
-        <v>7106306</v>
+        <v>7106373</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Sex blommor</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4648,12 +4648,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4664,32 +4664,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126862878</v>
+        <v>126868484</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691869</v>
+        <v>691825</v>
       </c>
       <c r="R41" t="n">
-        <v>7106348</v>
+        <v>7106372</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4737,6 +4737,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4749,12 +4754,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4765,10 +4770,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126868466</v>
+        <v>126867603</v>
       </c>
       <c r="B42" t="n">
-        <v>79050</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4776,21 +4781,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4805,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>692151</v>
+        <v>691608</v>
       </c>
       <c r="R42" t="n">
-        <v>7106586</v>
+        <v>7106686</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,12 +4855,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4866,32 +4871,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126862895</v>
+        <v>126865524</v>
       </c>
       <c r="B43" t="n">
-        <v>91904</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4906,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691850</v>
+        <v>691833</v>
       </c>
       <c r="R43" t="n">
-        <v>7106258</v>
+        <v>7106306</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4951,12 +4956,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4967,32 +4972,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126868311</v>
+        <v>126862878</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5002,10 +5007,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691808</v>
+        <v>691869</v>
       </c>
       <c r="R44" t="n">
-        <v>7106373</v>
+        <v>7106348</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5040,11 +5045,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Sex blommor</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5057,12 +5057,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5587,48 +5587,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126868092</v>
+        <v>126867680</v>
       </c>
       <c r="B50" t="n">
-        <v>80121</v>
+        <v>92620</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691959</v>
+        <v>691998</v>
       </c>
       <c r="R50" t="n">
-        <v>7106774</v>
+        <v>7106190</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5669,19 +5666,18 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5692,7 +5688,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126862868</v>
+        <v>126868092</v>
       </c>
       <c r="B51" t="n">
         <v>80121</v>
@@ -5721,16 +5717,19 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691831</v>
+        <v>691959</v>
       </c>
       <c r="R51" t="n">
-        <v>7106374</v>
+        <v>7106774</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5771,18 +5770,19 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5793,10 +5793,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126867609</v>
+        <v>126862868</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>80121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5804,21 +5804,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691764</v>
+        <v>691831</v>
       </c>
       <c r="R52" t="n">
-        <v>7106568</v>
+        <v>7106374</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5878,12 +5878,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5894,10 +5894,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126862888</v>
+        <v>126867609</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5905,21 +5905,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5929,10 +5929,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691826</v>
+        <v>691764</v>
       </c>
       <c r="R53" t="n">
-        <v>7106492</v>
+        <v>7106568</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,12 +5979,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5995,32 +5995,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126867680</v>
+        <v>126862888</v>
       </c>
       <c r="B54" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691998</v>
+        <v>691826</v>
       </c>
       <c r="R54" t="n">
-        <v>7106190</v>
+        <v>7106492</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6080,12 +6080,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6096,32 +6096,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126862880</v>
+        <v>126868319</v>
       </c>
       <c r="B55" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691805</v>
+        <v>691840</v>
       </c>
       <c r="R55" t="n">
-        <v>7106432</v>
+        <v>7106322</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6181,12 +6181,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126868319</v>
+        <v>126868482</v>
       </c>
       <c r="B56" t="n">
         <v>80121</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691840</v>
+        <v>691832</v>
       </c>
       <c r="R56" t="n">
-        <v>7106322</v>
+        <v>7106323</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,12 +6282,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126868482</v>
+        <v>126868302</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,21 +6309,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691832</v>
+        <v>691835</v>
       </c>
       <c r="R57" t="n">
-        <v>7106323</v>
+        <v>7106296</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,12 +6383,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6399,10 +6399,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126868302</v>
+        <v>126868321</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>80121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691835</v>
+        <v>691834</v>
       </c>
       <c r="R58" t="n">
-        <v>7106296</v>
+        <v>7106306</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6500,32 +6500,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126868321</v>
+        <v>126862880</v>
       </c>
       <c r="B59" t="n">
-        <v>80121</v>
+        <v>98447</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6535,10 +6535,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691834</v>
+        <v>691805</v>
       </c>
       <c r="R59" t="n">
-        <v>7106306</v>
+        <v>7106432</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6585,12 +6585,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126868507</v>
+        <v>126862856</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,21 +8155,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>691973</v>
+        <v>691712</v>
       </c>
       <c r="R75" t="n">
-        <v>7106021</v>
+        <v>7105968</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8229,12 +8229,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8245,7 +8245,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126867625</v>
+        <v>126868507</v>
       </c>
       <c r="B76" t="n">
         <v>79018</v>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>691792</v>
+        <v>691973</v>
       </c>
       <c r="R76" t="n">
-        <v>7106323</v>
+        <v>7106021</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8330,12 +8330,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8346,10 +8346,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126868317</v>
+        <v>126867625</v>
       </c>
       <c r="B77" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8357,21 +8357,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>691833</v>
+        <v>691792</v>
       </c>
       <c r="R77" t="n">
-        <v>7106362</v>
+        <v>7106323</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8419,11 +8419,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På  "sälg låga".</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8436,12 +8431,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8452,10 +8447,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126867613</v>
+        <v>126865527</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8463,21 +8458,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8487,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>691720</v>
+        <v>691852</v>
       </c>
       <c r="R78" t="n">
-        <v>7106626</v>
+        <v>7106251</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8537,12 +8532,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8553,10 +8548,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126867636</v>
+        <v>126868317</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8564,21 +8559,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>691954</v>
+        <v>691833</v>
       </c>
       <c r="R79" t="n">
-        <v>7106198</v>
+        <v>7106362</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8626,6 +8621,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På  "sälg låga".</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8638,12 +8638,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8654,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126865527</v>
+        <v>126867613</v>
       </c>
       <c r="B80" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,21 +8665,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>691852</v>
+        <v>691720</v>
       </c>
       <c r="R80" t="n">
-        <v>7106251</v>
+        <v>7106626</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8739,12 +8739,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8755,32 +8755,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126862883</v>
+        <v>126867636</v>
       </c>
       <c r="B81" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8790,10 +8790,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>691832</v>
+        <v>691954</v>
       </c>
       <c r="R81" t="n">
-        <v>7106475</v>
+        <v>7106198</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8840,12 +8840,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126862856</v>
+        <v>126862883</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>98447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>691712</v>
+        <v>691832</v>
       </c>
       <c r="R82" t="n">
-        <v>7105968</v>
+        <v>7106475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9374,10 +9374,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126867618</v>
+        <v>126862864</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>691826</v>
+        <v>691833</v>
       </c>
       <c r="R87" t="n">
-        <v>7106372</v>
+        <v>7106331</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9447,6 +9447,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Bohål i asp. 7-9 cm i diameter</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -9459,12 +9464,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9475,48 +9480,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126865721</v>
+        <v>126867618</v>
       </c>
       <c r="B88" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>691719</v>
+        <v>691826</v>
       </c>
       <c r="R88" t="n">
-        <v>7105959</v>
+        <v>7106372</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9557,19 +9559,18 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9580,45 +9581,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126868498</v>
+        <v>126865721</v>
       </c>
       <c r="B89" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>691899</v>
+        <v>691719</v>
       </c>
       <c r="R89" t="n">
-        <v>7106892</v>
+        <v>7105959</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9653,29 +9657,25 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Mycket på gammal gran</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9787,10 +9787,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126862864</v>
+        <v>126868498</v>
       </c>
       <c r="B91" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9798,21 +9798,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9822,10 +9822,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>691833</v>
+        <v>691899</v>
       </c>
       <c r="R91" t="n">
-        <v>7106331</v>
+        <v>7106892</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Bohål i asp. 7-9 cm i diameter</t>
+          <t>Mycket på gammal gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9877,12 +9877,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10512,32 +10512,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126868495</v>
+        <v>126862875</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>691968</v>
+        <v>691831</v>
       </c>
       <c r="R98" t="n">
-        <v>7106763</v>
+        <v>7106441</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10585,11 +10585,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -10602,12 +10597,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10618,10 +10613,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126867604</v>
+        <v>126854722</v>
       </c>
       <c r="B99" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10629,21 +10624,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10653,10 +10648,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>691739</v>
+        <v>691973</v>
       </c>
       <c r="R99" t="n">
-        <v>7106619</v>
+        <v>7106021</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10703,26 +10698,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126868491</v>
+        <v>126862865</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10730,21 +10721,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10754,10 +10745,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>691996</v>
+        <v>691711</v>
       </c>
       <c r="R100" t="n">
-        <v>7106674</v>
+        <v>7105963</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10804,12 +10795,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10820,32 +10811,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126862875</v>
+        <v>126868495</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10855,10 +10846,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>691831</v>
+        <v>691968</v>
       </c>
       <c r="R101" t="n">
-        <v>7106441</v>
+        <v>7106763</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10893,6 +10884,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -10905,12 +10901,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10921,10 +10917,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126854722</v>
+        <v>126867604</v>
       </c>
       <c r="B102" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10932,21 +10928,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10956,10 +10952,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>691973</v>
+        <v>691739</v>
       </c>
       <c r="R102" t="n">
-        <v>7106021</v>
+        <v>7106619</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11006,22 +11002,26 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126862865</v>
+        <v>126868491</v>
       </c>
       <c r="B103" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11029,21 +11029,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>691711</v>
+        <v>691996</v>
       </c>
       <c r="R103" t="n">
-        <v>7105963</v>
+        <v>7106674</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11103,12 +11103,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11119,32 +11119,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126868490</v>
+        <v>126859060</v>
       </c>
       <c r="B104" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11154,10 +11154,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>691832</v>
+        <v>691820</v>
       </c>
       <c r="R104" t="n">
-        <v>7106448</v>
+        <v>7106607</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11204,26 +11204,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126852559</v>
+        <v>126868490</v>
       </c>
       <c r="B105" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11231,21 +11227,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11255,10 +11251,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>691715</v>
+        <v>691832</v>
       </c>
       <c r="R105" t="n">
-        <v>7105958</v>
+        <v>7106448</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11305,44 +11301,48 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126859060</v>
+        <v>126852559</v>
       </c>
       <c r="B106" t="n">
-        <v>98468</v>
+        <v>79636</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11352,10 +11352,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>691820</v>
+        <v>691715</v>
       </c>
       <c r="R106" t="n">
-        <v>7106607</v>
+        <v>7105958</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14066,45 +14066,61 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126867655</v>
+        <v>126862860</v>
       </c>
       <c r="B133" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691840</v>
+        <v>691767</v>
       </c>
       <c r="R133" t="n">
-        <v>7105751</v>
+        <v>7105824</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14139,6 +14155,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Höna med kyckling</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -14151,12 +14172,12 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
@@ -14167,32 +14188,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126868338</v>
+        <v>126867655</v>
       </c>
       <c r="B134" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14202,10 +14223,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691750</v>
+        <v>691840</v>
       </c>
       <c r="R134" t="n">
-        <v>7105871</v>
+        <v>7105751</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14240,11 +14261,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Tre g:a fk.</t>
-        </is>
-      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
@@ -14257,12 +14273,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14273,10 +14289,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126862860</v>
+        <v>126868338</v>
       </c>
       <c r="B135" t="n">
-        <v>56853</v>
+        <v>92620</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14284,50 +14300,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691767</v>
+        <v>691750</v>
       </c>
       <c r="R135" t="n">
-        <v>7105824</v>
+        <v>7105871</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Höna med kyckling</t>
+          <t>Tre g:a fk.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14379,12 +14379,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14395,10 +14395,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126869124</v>
+        <v>126867654</v>
       </c>
       <c r="B136" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14406,37 +14406,37 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691841</v>
+        <v>691851</v>
       </c>
       <c r="R136" t="n">
-        <v>7105771</v>
+        <v>7105739</v>
       </c>
       <c r="S136" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14474,19 +14474,18 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14497,7 +14496,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126867654</v>
+        <v>126867668</v>
       </c>
       <c r="B137" t="n">
         <v>79018</v>
@@ -14532,10 +14531,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691851</v>
+        <v>691702</v>
       </c>
       <c r="R137" t="n">
-        <v>7105739</v>
+        <v>7105912</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14598,32 +14597,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126867668</v>
+        <v>126868475</v>
       </c>
       <c r="B138" t="n">
-        <v>79018</v>
+        <v>58492</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>208245</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14633,10 +14632,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691702</v>
+        <v>691770</v>
       </c>
       <c r="R138" t="n">
-        <v>7105912</v>
+        <v>7105834</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14683,12 +14682,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14699,32 +14698,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126868475</v>
+        <v>126863145</v>
       </c>
       <c r="B139" t="n">
-        <v>58492</v>
+        <v>79607</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208245</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14734,10 +14733,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691770</v>
+        <v>691819</v>
       </c>
       <c r="R139" t="n">
-        <v>7105834</v>
+        <v>7105865</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14784,12 +14783,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14800,10 +14799,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126863145</v>
+        <v>126869124</v>
       </c>
       <c r="B140" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14811,37 +14810,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691819</v>
+        <v>691841</v>
       </c>
       <c r="R140" t="n">
-        <v>7105865</v>
+        <v>7105771</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14879,18 +14878,19 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -15507,10 +15507,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126862181</v>
+        <v>126862172</v>
       </c>
       <c r="B147" t="n">
-        <v>78777</v>
+        <v>91330</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15518,21 +15518,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15542,10 +15542,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691865</v>
+        <v>691876</v>
       </c>
       <c r="R147" t="n">
-        <v>7105739</v>
+        <v>7105714</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15608,10 +15608,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126862172</v>
+        <v>126862181</v>
       </c>
       <c r="B148" t="n">
-        <v>91330</v>
+        <v>78777</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15619,21 +15619,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>691876</v>
+        <v>691865</v>
       </c>
       <c r="R148" t="n">
-        <v>7105714</v>
+        <v>7105739</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15709,10 +15709,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126868301</v>
+        <v>126862471</v>
       </c>
       <c r="B149" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15720,21 +15720,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15744,10 +15744,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>691717</v>
+        <v>691883</v>
       </c>
       <c r="R149" t="n">
-        <v>7105891</v>
+        <v>7105746</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15794,26 +15794,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126867670</v>
+        <v>126868301</v>
       </c>
       <c r="B150" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15821,21 +15817,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15845,10 +15841,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>691697</v>
+        <v>691717</v>
       </c>
       <c r="R150" t="n">
-        <v>7105917</v>
+        <v>7105891</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15895,12 +15891,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15911,7 +15907,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126867659</v>
+        <v>126867670</v>
       </c>
       <c r="B151" t="n">
         <v>79018</v>
@@ -15946,10 +15942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691800</v>
+        <v>691697</v>
       </c>
       <c r="R151" t="n">
-        <v>7105765</v>
+        <v>7105917</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16012,10 +16008,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126862205</v>
+        <v>126867659</v>
       </c>
       <c r="B152" t="n">
-        <v>82859</v>
+        <v>79018</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16023,21 +16019,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16047,10 +16043,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691964</v>
+        <v>691800</v>
       </c>
       <c r="R152" t="n">
-        <v>7105748</v>
+        <v>7105765</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16097,12 +16093,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -16113,10 +16109,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126862471</v>
+        <v>126862205</v>
       </c>
       <c r="B153" t="n">
-        <v>79018</v>
+        <v>82859</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16124,21 +16120,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16148,10 +16144,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691883</v>
+        <v>691964</v>
       </c>
       <c r="R153" t="n">
-        <v>7105746</v>
+        <v>7105748</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16198,22 +16194,26 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126868476</v>
+        <v>126868305</v>
       </c>
       <c r="B154" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16221,21 +16221,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16245,10 +16245,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691786</v>
+        <v>691870</v>
       </c>
       <c r="R154" t="n">
-        <v>7105813</v>
+        <v>7105761</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16295,12 +16295,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16311,10 +16311,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126868305</v>
+        <v>126868476</v>
       </c>
       <c r="B155" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16322,21 +16322,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16346,10 +16346,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691870</v>
+        <v>691786</v>
       </c>
       <c r="R155" t="n">
-        <v>7105761</v>
+        <v>7105813</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16396,12 +16396,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -17545,45 +17545,57 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126862170</v>
+        <v>126862862</v>
       </c>
       <c r="B167" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691866</v>
+        <v>691772</v>
       </c>
       <c r="R167" t="n">
-        <v>7105795</v>
+        <v>7105816</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17618,6 +17630,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>Flygfärdig kyckling med höna</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -17630,12 +17647,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17646,32 +17663,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126868470</v>
+        <v>126862465</v>
       </c>
       <c r="B168" t="n">
-        <v>79636</v>
+        <v>98468</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17681,10 +17698,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691906</v>
+        <v>691913</v>
       </c>
       <c r="R168" t="n">
-        <v>7105789</v>
+        <v>7105810</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17719,6 +17736,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>&gt;10 ex</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17731,73 +17753,57 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126862862</v>
+        <v>126868470</v>
       </c>
       <c r="B169" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691772</v>
+        <v>691906</v>
       </c>
       <c r="R169" t="n">
-        <v>7105816</v>
+        <v>7105789</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17832,11 +17838,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Flygfärdig kyckling med höna</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17849,12 +17850,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17865,32 +17866,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126862465</v>
+        <v>126862170</v>
       </c>
       <c r="B170" t="n">
-        <v>98468</v>
+        <v>79636</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17900,10 +17901,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691913</v>
+        <v>691866</v>
       </c>
       <c r="R170" t="n">
-        <v>7105810</v>
+        <v>7105795</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17938,11 +17939,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>&gt;10 ex</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -17955,15 +17951,19 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18169,10 +18169,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126868509</v>
+        <v>126863153</v>
       </c>
       <c r="B173" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18180,21 +18180,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18204,10 +18204,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691892</v>
+        <v>691843</v>
       </c>
       <c r="R173" t="n">
-        <v>7105763</v>
+        <v>7105861</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18242,11 +18242,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ganska mycket på tallarna</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -18259,12 +18254,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18275,7 +18270,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126867642</v>
+        <v>126868509</v>
       </c>
       <c r="B174" t="n">
         <v>79018</v>
@@ -18310,10 +18305,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691963</v>
+        <v>691892</v>
       </c>
       <c r="R174" t="n">
-        <v>7105736</v>
+        <v>7105763</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18348,6 +18343,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ganska mycket på tallarna</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18360,12 +18360,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18376,10 +18376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126869131</v>
+        <v>126867642</v>
       </c>
       <c r="B175" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18387,37 +18387,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691873</v>
+        <v>691963</v>
       </c>
       <c r="R175" t="n">
-        <v>7105745</v>
+        <v>7105736</v>
       </c>
       <c r="S175" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18461,12 +18461,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18477,10 +18477,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126863153</v>
+        <v>126869131</v>
       </c>
       <c r="B176" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18488,37 +18488,37 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691843</v>
+        <v>691873</v>
       </c>
       <c r="R176" t="n">
-        <v>7105861</v>
+        <v>7105745</v>
       </c>
       <c r="S176" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -18562,12 +18562,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -19299,32 +19299,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>126862871</v>
+        <v>126867661</v>
       </c>
       <c r="B184" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19334,10 +19334,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>691713</v>
+        <v>691743</v>
       </c>
       <c r="R184" t="n">
-        <v>7105893</v>
+        <v>7105870</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19384,12 +19384,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19400,32 +19400,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>126867661</v>
+        <v>126862871</v>
       </c>
       <c r="B185" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19435,10 +19435,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>691743</v>
+        <v>691713</v>
       </c>
       <c r="R185" t="n">
-        <v>7105870</v>
+        <v>7105893</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19485,12 +19485,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -20504,10 +20504,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126868499</v>
+        <v>126868478</v>
       </c>
       <c r="B196" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -20515,21 +20515,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20539,10 +20539,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>691849</v>
+        <v>692202</v>
       </c>
       <c r="R196" t="n">
-        <v>7106968</v>
+        <v>7106954</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20575,11 +20575,6 @@
       <c r="AA196" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -20610,49 +20605,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126868471</v>
+        <v>126862180</v>
       </c>
       <c r="B197" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>692149</v>
+        <v>692178</v>
       </c>
       <c r="R197" t="n">
-        <v>7106995</v>
+        <v>7107022</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20687,11 +20678,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
@@ -20704,12 +20690,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -20720,7 +20706,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126868478</v>
+        <v>126863150</v>
       </c>
       <c r="B198" t="n">
         <v>78777</v>
@@ -20755,10 +20741,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>692202</v>
+        <v>693008</v>
       </c>
       <c r="R198" t="n">
-        <v>7106954</v>
+        <v>7105846</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20805,12 +20791,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -20821,10 +20807,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126862180</v>
+        <v>126868499</v>
       </c>
       <c r="B199" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20832,21 +20818,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20856,10 +20842,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>692178</v>
+        <v>691849</v>
       </c>
       <c r="R199" t="n">
-        <v>7107022</v>
+        <v>7106968</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20894,6 +20880,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
@@ -20906,12 +20897,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -20922,45 +20913,49 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126863150</v>
+        <v>126868471</v>
       </c>
       <c r="B200" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>693008</v>
+        <v>692149</v>
       </c>
       <c r="R200" t="n">
-        <v>7105846</v>
+        <v>7106995</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20995,6 +20990,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -21007,12 +21007,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -23051,45 +23051,48 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>126868467</v>
+        <v>126867920</v>
       </c>
       <c r="B221" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>692244</v>
+        <v>692149</v>
       </c>
       <c r="R221" t="n">
-        <v>7106923</v>
+        <v>7107005</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23130,70 +23133,64 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>126867920</v>
+        <v>126868467</v>
       </c>
       <c r="B222" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>692149</v>
+        <v>692244</v>
       </c>
       <c r="R222" t="n">
-        <v>7107005</v>
+        <v>7106923</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23234,22 +23231,25 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
-      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24260,48 +24260,48 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>126869134</v>
+        <v>126862475</v>
       </c>
       <c r="B233" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691806</v>
+        <v>692904</v>
       </c>
       <c r="R233" t="n">
-        <v>7107033</v>
+        <v>7105978</v>
       </c>
       <c r="S233" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24345,64 +24345,60 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY233" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>126862475</v>
+        <v>126869134</v>
       </c>
       <c r="B234" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>692904</v>
+        <v>691806</v>
       </c>
       <c r="R234" t="n">
-        <v>7105978</v>
+        <v>7107033</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -24446,15 +24442,19 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY234" t="inlineStr"/>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">

--- a/artfynd/A 31135-2024 artfynd.xlsx
+++ b/artfynd/A 31135-2024 artfynd.xlsx
@@ -996,48 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126867049</v>
+        <v>126868496</v>
       </c>
       <c r="B5" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691961</v>
+        <v>691941</v>
       </c>
       <c r="R5" t="n">
-        <v>7106020</v>
+        <v>7106860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,19 +1075,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1101,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126865523</v>
+        <v>126862876</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691797</v>
+        <v>691847</v>
       </c>
       <c r="R6" t="n">
-        <v>7106375</v>
+        <v>7106392</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1182,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1202,32 +1198,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126868503</v>
+        <v>126862884</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692149</v>
+        <v>691817</v>
       </c>
       <c r="R7" t="n">
-        <v>7106588</v>
+        <v>7106456</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,12 +1283,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1303,45 +1299,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126868496</v>
+        <v>126867049</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691941</v>
+        <v>691961</v>
       </c>
       <c r="R8" t="n">
-        <v>7106860</v>
+        <v>7106020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,18 +1381,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1404,32 +1404,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126862876</v>
+        <v>126865523</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691847</v>
+        <v>691797</v>
       </c>
       <c r="R9" t="n">
-        <v>7106392</v>
+        <v>7106375</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1489,12 +1489,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1505,32 +1505,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126862884</v>
+        <v>126868503</v>
       </c>
       <c r="B10" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691817</v>
+        <v>692149</v>
       </c>
       <c r="R10" t="n">
-        <v>7106456</v>
+        <v>7106588</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,12 +1590,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -4765,32 +4765,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126862878</v>
+        <v>126867616</v>
       </c>
       <c r="B42" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691869</v>
+        <v>691811</v>
       </c>
       <c r="R42" t="n">
-        <v>7106348</v>
+        <v>7106492</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4850,12 +4850,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4866,32 +4866,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126868311</v>
+        <v>126862878</v>
       </c>
       <c r="B43" t="n">
-        <v>98469</v>
+        <v>98448</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691808</v>
+        <v>691869</v>
       </c>
       <c r="R43" t="n">
-        <v>7106373</v>
+        <v>7106348</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,11 +4939,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Sex blommor</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4956,12 +4951,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4972,32 +4967,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126867616</v>
+        <v>126868311</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5007,10 +5002,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691811</v>
+        <v>691808</v>
       </c>
       <c r="R44" t="n">
-        <v>7106492</v>
+        <v>7106373</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,6 +5040,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sex blommor</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5057,12 +5057,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6096,32 +6096,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126867615</v>
+        <v>126862880</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691809</v>
+        <v>691805</v>
       </c>
       <c r="R55" t="n">
-        <v>7106514</v>
+        <v>7106432</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6181,12 +6181,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6197,32 +6197,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126862880</v>
+        <v>126868319</v>
       </c>
       <c r="B56" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691805</v>
+        <v>691840</v>
       </c>
       <c r="R56" t="n">
-        <v>7106432</v>
+        <v>7106322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6282,12 +6282,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126868319</v>
+        <v>126867615</v>
       </c>
       <c r="B57" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6309,21 +6309,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6333,10 +6333,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691840</v>
+        <v>691809</v>
       </c>
       <c r="R57" t="n">
-        <v>7106322</v>
+        <v>7106514</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6383,12 +6383,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6702,32 +6702,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126868488</v>
+        <v>126867592</v>
       </c>
       <c r="B61" t="n">
-        <v>98448</v>
+        <v>79042</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6434</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6737,10 +6737,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691828</v>
+        <v>691747</v>
       </c>
       <c r="R61" t="n">
-        <v>7106415</v>
+        <v>7106703</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6775,11 +6775,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Blommande</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6792,12 +6787,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6808,32 +6803,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126865528</v>
+        <v>126868320</v>
       </c>
       <c r="B62" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6843,10 +6838,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691813</v>
+        <v>691833</v>
       </c>
       <c r="R62" t="n">
-        <v>7106581</v>
+        <v>7106302</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6881,6 +6876,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt gammal grövre sälg.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6893,12 +6893,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6909,32 +6909,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126867592</v>
+        <v>126868316</v>
       </c>
       <c r="B63" t="n">
-        <v>79042</v>
+        <v>80121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,10 +6944,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691747</v>
+        <v>691796</v>
       </c>
       <c r="R63" t="n">
-        <v>7106703</v>
+        <v>7106376</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6982,6 +6982,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt gammal sälg intill hyggeskant.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6994,12 +6999,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7010,32 +7015,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126867634</v>
+        <v>126868488</v>
       </c>
       <c r="B64" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7045,10 +7050,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>691888</v>
+        <v>691828</v>
       </c>
       <c r="R64" t="n">
-        <v>7106163</v>
+        <v>7106415</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7083,6 +7088,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Blommande</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7095,12 +7105,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7111,32 +7121,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126862892</v>
+        <v>126865528</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7156,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691871</v>
+        <v>691813</v>
       </c>
       <c r="R65" t="n">
-        <v>7106324</v>
+        <v>7106581</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7196,12 +7206,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7212,10 +7222,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126862176</v>
+        <v>126867634</v>
       </c>
       <c r="B66" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7223,42 +7233,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>692001</v>
+        <v>691888</v>
       </c>
       <c r="R66" t="n">
-        <v>7106695</v>
+        <v>7106163</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,12 +7307,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7321,10 +7323,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126868316</v>
+        <v>126867623</v>
       </c>
       <c r="B67" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7332,21 +7334,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7356,10 +7358,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691796</v>
+        <v>691797</v>
       </c>
       <c r="R67" t="n">
-        <v>7106376</v>
+        <v>7106341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7394,11 +7396,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt gammal sälg intill hyggeskant.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7411,12 +7408,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7427,10 +7424,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126868320</v>
+        <v>126868328</v>
       </c>
       <c r="B68" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7438,21 +7435,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7462,10 +7459,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691833</v>
+        <v>691816</v>
       </c>
       <c r="R68" t="n">
-        <v>7106302</v>
+        <v>7106552</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7502,7 +7499,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt gammal grövre sälg.</t>
+          <t>På äldre tall.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7533,7 +7530,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126867623</v>
+        <v>126862892</v>
       </c>
       <c r="B69" t="n">
         <v>79018</v>
@@ -7568,10 +7565,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691797</v>
+        <v>691871</v>
       </c>
       <c r="R69" t="n">
-        <v>7106341</v>
+        <v>7106324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7618,12 +7615,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7634,10 +7631,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126868328</v>
+        <v>126862176</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7645,34 +7642,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>691816</v>
+        <v>692001</v>
       </c>
       <c r="R70" t="n">
-        <v>7106552</v>
+        <v>7106695</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7707,11 +7712,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På äldre tall.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7724,12 +7724,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126868507</v>
+        <v>126865527</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8155,21 +8155,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>691973</v>
+        <v>691852</v>
       </c>
       <c r="R75" t="n">
-        <v>7106021</v>
+        <v>7106251</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8229,12 +8229,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8245,10 +8245,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126867613</v>
+        <v>126868317</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>691720</v>
+        <v>691833</v>
       </c>
       <c r="R76" t="n">
-        <v>7106626</v>
+        <v>7106362</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8318,6 +8318,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På  "sälg låga".</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8330,12 +8335,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8346,7 +8351,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126867636</v>
+        <v>126867613</v>
       </c>
       <c r="B77" t="n">
         <v>79018</v>
@@ -8381,10 +8386,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>691954</v>
+        <v>691720</v>
       </c>
       <c r="R77" t="n">
-        <v>7106198</v>
+        <v>7106626</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8447,7 +8452,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126867625</v>
+        <v>126867636</v>
       </c>
       <c r="B78" t="n">
         <v>79018</v>
@@ -8482,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>691792</v>
+        <v>691954</v>
       </c>
       <c r="R78" t="n">
-        <v>7106323</v>
+        <v>7106198</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8548,32 +8553,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126862883</v>
+        <v>126867625</v>
       </c>
       <c r="B79" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8583,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>691832</v>
+        <v>691792</v>
       </c>
       <c r="R79" t="n">
-        <v>7106475</v>
+        <v>7106323</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8633,12 +8638,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8649,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126865527</v>
+        <v>126862856</v>
       </c>
       <c r="B80" t="n">
-        <v>80121</v>
+        <v>79607</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8660,21 +8665,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8684,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>691852</v>
+        <v>691712</v>
       </c>
       <c r="R80" t="n">
-        <v>7106251</v>
+        <v>7105968</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8734,12 +8739,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8750,10 +8755,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126868317</v>
+        <v>126868507</v>
       </c>
       <c r="B81" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8761,21 +8766,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8785,10 +8790,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>691833</v>
+        <v>691973</v>
       </c>
       <c r="R81" t="n">
-        <v>7106362</v>
+        <v>7106021</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8823,11 +8828,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På  "sälg låga".</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8840,12 +8840,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126862856</v>
+        <v>126862883</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>98448</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>691712</v>
+        <v>691832</v>
       </c>
       <c r="R82" t="n">
-        <v>7105968</v>
+        <v>7106475</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8957,32 +8957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126865530</v>
+        <v>126867627</v>
       </c>
       <c r="B83" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>691847</v>
+        <v>691826</v>
       </c>
       <c r="R83" t="n">
-        <v>7106512</v>
+        <v>7106291</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9042,12 +9042,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -9058,7 +9058,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126867627</v>
+        <v>126868492</v>
       </c>
       <c r="B84" t="n">
         <v>79018</v>
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>691826</v>
+        <v>692005</v>
       </c>
       <c r="R84" t="n">
-        <v>7106291</v>
+        <v>7106694</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9143,12 +9143,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9159,45 +9159,53 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126868492</v>
+        <v>126862859</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>692005</v>
+        <v>691967</v>
       </c>
       <c r="R85" t="n">
-        <v>7106694</v>
+        <v>7106021</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9232,6 +9240,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Solgrop och tjäderspillning</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9244,12 +9257,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9260,53 +9273,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126862859</v>
+        <v>126865530</v>
       </c>
       <c r="B86" t="n">
-        <v>56853</v>
+        <v>98448</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>691967</v>
+        <v>691847</v>
       </c>
       <c r="R86" t="n">
-        <v>7106021</v>
+        <v>7106512</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9341,11 +9346,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Solgrop och tjäderspillning</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -9358,12 +9358,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Elin Kannerby, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9374,10 +9374,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126868498</v>
+        <v>126862864</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9385,21 +9385,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9409,10 +9409,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>691899</v>
+        <v>691833</v>
       </c>
       <c r="R87" t="n">
-        <v>7106892</v>
+        <v>7106331</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Mycket på gammal gran</t>
+          <t>Bohål i asp. 7-9 cm i diameter</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9464,12 +9464,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9480,45 +9480,48 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126867618</v>
+        <v>126865721</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>691826</v>
+        <v>691719</v>
       </c>
       <c r="R88" t="n">
-        <v>7106372</v>
+        <v>7105959</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9559,18 +9562,19 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9581,32 +9585,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126868324</v>
+        <v>126867605</v>
       </c>
       <c r="B89" t="n">
-        <v>98448</v>
+        <v>80121</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9616,10 +9620,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>691829</v>
+        <v>691806</v>
       </c>
       <c r="R89" t="n">
-        <v>7106436</v>
+        <v>7106380</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9654,11 +9658,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>1 blomma + några ytterligare plantor.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -9671,12 +9670,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9687,10 +9686,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126862864</v>
+        <v>126868498</v>
       </c>
       <c r="B90" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9698,21 +9697,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9722,10 +9721,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>691833</v>
+        <v>691899</v>
       </c>
       <c r="R90" t="n">
-        <v>7106331</v>
+        <v>7106892</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9762,7 +9761,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Bohål i asp. 7-9 cm i diameter</t>
+          <t>Mycket på gammal gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9777,12 +9776,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9793,48 +9792,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126865721</v>
+        <v>126867618</v>
       </c>
       <c r="B91" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>691719</v>
+        <v>691826</v>
       </c>
       <c r="R91" t="n">
-        <v>7105959</v>
+        <v>7106372</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9875,19 +9871,18 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9898,10 +9893,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126867605</v>
+        <v>126869126</v>
       </c>
       <c r="B92" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9909,37 +9904,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>691806</v>
+        <v>691973</v>
       </c>
       <c r="R92" t="n">
-        <v>7106380</v>
+        <v>7106774</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9983,12 +9986,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9999,56 +10002,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126869126</v>
+        <v>126868324</v>
       </c>
       <c r="B93" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>691973</v>
+        <v>691829</v>
       </c>
       <c r="R93" t="n">
-        <v>7106774</v>
+        <v>7106436</v>
       </c>
       <c r="S93" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10078,6 +10073,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>1 blomma + några ytterligare plantor.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10092,12 +10092,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10310,32 +10310,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126862894</v>
+        <v>126862885</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10345,10 +10345,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>692038</v>
+        <v>691817</v>
       </c>
       <c r="R96" t="n">
-        <v>7106130</v>
+        <v>7106411</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10411,32 +10411,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126862885</v>
+        <v>126862894</v>
       </c>
       <c r="B97" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10446,10 +10446,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>691817</v>
+        <v>692038</v>
       </c>
       <c r="R97" t="n">
-        <v>7106411</v>
+        <v>7106130</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10512,10 +10512,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126854722</v>
+        <v>126867604</v>
       </c>
       <c r="B98" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10523,21 +10523,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>691973</v>
+        <v>691739</v>
       </c>
       <c r="R98" t="n">
-        <v>7106021</v>
+        <v>7106619</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10597,22 +10597,26 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126862865</v>
+        <v>126868491</v>
       </c>
       <c r="B99" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10620,21 +10624,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10644,10 +10648,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>691711</v>
+        <v>691996</v>
       </c>
       <c r="R99" t="n">
-        <v>7105963</v>
+        <v>7106674</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10694,12 +10698,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10710,10 +10714,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126867604</v>
+        <v>126868495</v>
       </c>
       <c r="B100" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10721,21 +10725,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10745,10 +10749,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>691739</v>
+        <v>691968</v>
       </c>
       <c r="R100" t="n">
-        <v>7106619</v>
+        <v>7106763</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10783,6 +10787,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -10795,12 +10804,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10811,32 +10820,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126868495</v>
+        <v>126862875</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10846,10 +10855,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>691968</v>
+        <v>691831</v>
       </c>
       <c r="R101" t="n">
-        <v>7106763</v>
+        <v>7106441</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10884,11 +10893,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -10901,12 +10905,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10917,32 +10921,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126862875</v>
+        <v>126854722</v>
       </c>
       <c r="B102" t="n">
-        <v>98448</v>
+        <v>78777</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10952,10 +10956,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>691831</v>
+        <v>691973</v>
       </c>
       <c r="R102" t="n">
-        <v>7106441</v>
+        <v>7106021</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11002,26 +11006,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126868491</v>
+        <v>126862865</v>
       </c>
       <c r="B103" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11029,21 +11029,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11053,10 +11053,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>691996</v>
+        <v>691711</v>
       </c>
       <c r="R103" t="n">
-        <v>7106674</v>
+        <v>7105963</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11103,12 +11103,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12117,7 +12117,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126867614</v>
+        <v>126868493</v>
       </c>
       <c r="B114" t="n">
         <v>79018</v>
@@ -12152,10 +12152,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>691757</v>
+        <v>691997</v>
       </c>
       <c r="R114" t="n">
-        <v>7106584</v>
+        <v>7106738</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12202,12 +12202,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12218,7 +12218,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126868493</v>
+        <v>126867632</v>
       </c>
       <c r="B115" t="n">
         <v>79018</v>
@@ -12253,10 +12253,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>691997</v>
+        <v>691815</v>
       </c>
       <c r="R115" t="n">
-        <v>7106738</v>
+        <v>7106269</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12303,12 +12303,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -12319,27 +12319,27 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126867632</v>
+        <v>126856407</v>
       </c>
       <c r="B116" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>691815</v>
+        <v>692211</v>
       </c>
       <c r="R116" t="n">
-        <v>7106269</v>
+        <v>7106863</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12404,61 +12404,65 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126856407</v>
+        <v>126862177</v>
       </c>
       <c r="B117" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>692211</v>
+        <v>692018</v>
       </c>
       <c r="R117" t="n">
-        <v>7106863</v>
+        <v>7106688</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12505,65 +12509,61 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126862177</v>
+        <v>126868325</v>
       </c>
       <c r="B118" t="n">
-        <v>57661</v>
+        <v>98448</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>692018</v>
+        <v>691824</v>
       </c>
       <c r="R118" t="n">
-        <v>7106688</v>
+        <v>7106438</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12598,6 +12598,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>1 blomma.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -12610,12 +12615,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
@@ -12626,32 +12631,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126868325</v>
+        <v>126867614</v>
       </c>
       <c r="B119" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12661,10 +12666,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>691824</v>
+        <v>691757</v>
       </c>
       <c r="R119" t="n">
-        <v>7106438</v>
+        <v>7106584</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12699,11 +12704,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>1 blomma.</t>
-        </is>
-      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -12716,12 +12716,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -17545,57 +17545,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126862862</v>
+        <v>126868470</v>
       </c>
       <c r="B167" t="n">
-        <v>56853</v>
+        <v>79636</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691772</v>
+        <v>691906</v>
       </c>
       <c r="R167" t="n">
-        <v>7105816</v>
+        <v>7105789</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17630,11 +17618,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC167" t="inlineStr">
-        <is>
-          <t>Flygfärdig kyckling med höna</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
@@ -17647,12 +17630,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17663,32 +17646,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126862465</v>
+        <v>126862170</v>
       </c>
       <c r="B168" t="n">
-        <v>98469</v>
+        <v>79636</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17698,10 +17681,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691913</v>
+        <v>691866</v>
       </c>
       <c r="R168" t="n">
-        <v>7105810</v>
+        <v>7105795</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17736,11 +17719,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>&gt;10 ex</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -17753,57 +17731,73 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY168" t="inlineStr"/>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126868470</v>
+        <v>126862862</v>
       </c>
       <c r="B169" t="n">
-        <v>79636</v>
+        <v>56853</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691906</v>
+        <v>691772</v>
       </c>
       <c r="R169" t="n">
-        <v>7105789</v>
+        <v>7105816</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17838,6 +17832,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Flygfärdig kyckling med höna</t>
+        </is>
+      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
@@ -17850,12 +17849,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17866,32 +17865,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126862170</v>
+        <v>126862465</v>
       </c>
       <c r="B170" t="n">
-        <v>79636</v>
+        <v>98469</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17901,10 +17900,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691866</v>
+        <v>691913</v>
       </c>
       <c r="R170" t="n">
-        <v>7105795</v>
+        <v>7105810</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17939,6 +17938,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>&gt;10 ex</t>
+        </is>
+      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -17951,26 +17955,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126867644</v>
+        <v>126868315</v>
       </c>
       <c r="B171" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17978,21 +17978,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18002,10 +18002,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691975</v>
+        <v>691875</v>
       </c>
       <c r="R171" t="n">
-        <v>7105718</v>
+        <v>7105775</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18052,12 +18052,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18068,10 +18068,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126868315</v>
+        <v>126867644</v>
       </c>
       <c r="B172" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18079,21 +18079,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18103,10 +18103,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691875</v>
+        <v>691975</v>
       </c>
       <c r="R172" t="n">
-        <v>7105775</v>
+        <v>7105718</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18153,12 +18153,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -18169,10 +18169,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126868509</v>
+        <v>126869131</v>
       </c>
       <c r="B173" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18180,37 +18180,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691892</v>
+        <v>691873</v>
       </c>
       <c r="R173" t="n">
-        <v>7105763</v>
+        <v>7105745</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18240,11 +18240,6 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ganska mycket på tallarna</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18259,12 +18254,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18275,7 +18270,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126867642</v>
+        <v>126868509</v>
       </c>
       <c r="B174" t="n">
         <v>79018</v>
@@ -18310,10 +18305,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691963</v>
+        <v>691892</v>
       </c>
       <c r="R174" t="n">
-        <v>7105736</v>
+        <v>7105763</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18348,6 +18343,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Ganska mycket på tallarna</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -18360,12 +18360,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18376,10 +18376,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126869131</v>
+        <v>126867642</v>
       </c>
       <c r="B175" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18387,37 +18387,37 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691873</v>
+        <v>691963</v>
       </c>
       <c r="R175" t="n">
-        <v>7105745</v>
+        <v>7105736</v>
       </c>
       <c r="S175" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18461,12 +18461,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18578,32 +18578,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126862200</v>
+        <v>126868337</v>
       </c>
       <c r="B177" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691893</v>
+        <v>691763</v>
       </c>
       <c r="R177" t="n">
-        <v>7105722</v>
+        <v>7105866</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18651,6 +18651,11 @@
           <t>2025-07-23</t>
         </is>
       </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>4 g:a fk.</t>
+        </is>
+      </c>
       <c r="AD177" t="b">
         <v>0</v>
       </c>
@@ -18663,12 +18668,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18679,7 +18684,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126867648</v>
+        <v>126862200</v>
       </c>
       <c r="B178" t="n">
         <v>79018</v>
@@ -18714,10 +18719,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691932</v>
+        <v>691893</v>
       </c>
       <c r="R178" t="n">
-        <v>7105700</v>
+        <v>7105722</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18764,12 +18769,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Lise Mortensen</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18780,32 +18785,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126868337</v>
+        <v>126867648</v>
       </c>
       <c r="B179" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18815,10 +18820,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>691763</v>
+        <v>691932</v>
       </c>
       <c r="R179" t="n">
-        <v>7105866</v>
+        <v>7105700</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18853,11 +18858,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>4 g:a fk.</t>
-        </is>
-      </c>
       <c r="AD179" t="b">
         <v>0</v>
       </c>
@@ -18870,12 +18870,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lise Mortensen</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin</t>
+          <t>Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -20610,45 +20610,49 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>126868478</v>
+        <v>126868471</v>
       </c>
       <c r="B197" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>692202</v>
+        <v>692149</v>
       </c>
       <c r="R197" t="n">
-        <v>7106954</v>
+        <v>7106995</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20681,6 +20685,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -20711,7 +20720,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>126862180</v>
+        <v>126868478</v>
       </c>
       <c r="B198" t="n">
         <v>78777</v>
@@ -20746,10 +20755,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>692178</v>
+        <v>692202</v>
       </c>
       <c r="R198" t="n">
-        <v>7107022</v>
+        <v>7106954</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20796,12 +20805,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -20812,7 +20821,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126863150</v>
+        <v>126862180</v>
       </c>
       <c r="B199" t="n">
         <v>78777</v>
@@ -20847,10 +20856,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>693008</v>
+        <v>692178</v>
       </c>
       <c r="R199" t="n">
-        <v>7105846</v>
+        <v>7107022</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20897,12 +20906,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -20913,49 +20922,45 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126868471</v>
+        <v>126863150</v>
       </c>
       <c r="B200" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>692149</v>
+        <v>693008</v>
       </c>
       <c r="R200" t="n">
-        <v>7106995</v>
+        <v>7105846</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20990,11 +20995,6 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>1 uppflygande hane. Hittade även tjädertuppfjädrar intill grop i närheten.</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -21007,12 +21007,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -23051,48 +23051,45 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>126867920</v>
+        <v>126868467</v>
       </c>
       <c r="B221" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Tallvättsåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>692149</v>
+        <v>692244</v>
       </c>
       <c r="R221" t="n">
-        <v>7107005</v>
+        <v>7106923</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23133,64 +23130,70 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
+          <t>Beke Regelin</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Emil Lindgren</t>
-        </is>
-      </c>
-      <c r="AY221" t="inlineStr"/>
+          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
+        </is>
+      </c>
+      <c r="AY221" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>126868467</v>
+        <v>126867920</v>
       </c>
       <c r="B222" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tallvättsåsen, Ång</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>692244</v>
+        <v>692149</v>
       </c>
       <c r="R222" t="n">
-        <v>7106923</v>
+        <v>7107005</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23231,25 +23234,22 @@
       <c r="AE222" t="b">
         <v>0</v>
       </c>
+      <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Beke Regelin</t>
+          <t>Emil Lindgren</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Beke Regelin, Nicklas Gustavsson, Lars-Erik Nilsson, Isac Enetjärn, Elin Kannerby, Lise Mortensen, Miriam Schenk, Lisa Requin, Emil Lindgren, Peter Andersson, Maria  Persbo</t>
-        </is>
-      </c>
-      <c r="AY222" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23451,32 +23451,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>126862469</v>
+        <v>126863166</v>
       </c>
       <c r="B225" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23486,10 +23486,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>692662</v>
+        <v>692777</v>
       </c>
       <c r="R225" t="n">
-        <v>7105938</v>
+        <v>7105991</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23536,19 +23536,23 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY225" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>126863161</v>
+        <v>126862469</v>
       </c>
       <c r="B226" t="n">
         <v>79018</v>
@@ -23583,10 +23587,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>692910</v>
+        <v>692662</v>
       </c>
       <c r="R226" t="n">
-        <v>7106010</v>
+        <v>7105938</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23633,23 +23637,19 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY226" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>126862470</v>
+        <v>126863161</v>
       </c>
       <c r="B227" t="n">
         <v>79018</v>
@@ -23684,10 +23684,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>692986</v>
+        <v>692910</v>
       </c>
       <c r="R227" t="n">
-        <v>7105811</v>
+        <v>7106010</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23734,44 +23734,48 @@
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY227" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>126863166</v>
+        <v>126862470</v>
       </c>
       <c r="B228" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23781,10 +23785,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>692777</v>
+        <v>692986</v>
       </c>
       <c r="R228" t="n">
-        <v>7105991</v>
+        <v>7105811</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23831,26 +23835,22 @@
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY228" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>126862198</v>
+        <v>126869138</v>
       </c>
       <c r="B229" t="n">
-        <v>80156</v>
+        <v>92620</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -23858,37 +23858,37 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>692221</v>
+        <v>692139</v>
       </c>
       <c r="R229" t="n">
-        <v>7106885</v>
+        <v>7106987</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -23926,19 +23926,18 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
       <c r="AT229" t="inlineStr"/>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
@@ -23949,10 +23948,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>126862174</v>
+        <v>126863151</v>
       </c>
       <c r="B230" t="n">
-        <v>57821</v>
+        <v>78777</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -23960,42 +23959,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="K230" t="inlineStr"/>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691869</v>
+        <v>692957</v>
       </c>
       <c r="R230" t="n">
-        <v>7106950</v>
+        <v>7105907</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24042,12 +24033,12 @@
       <c r="AT230" t="inlineStr"/>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
@@ -24058,10 +24049,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>126869138</v>
+        <v>126862198</v>
       </c>
       <c r="B231" t="n">
-        <v>92620</v>
+        <v>80156</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -24069,37 +24060,37 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>692139</v>
+        <v>692221</v>
       </c>
       <c r="R231" t="n">
-        <v>7106987</v>
+        <v>7106885</v>
       </c>
       <c r="S231" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -24137,18 +24128,19 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
@@ -24159,10 +24151,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>126863151</v>
+        <v>126862174</v>
       </c>
       <c r="B232" t="n">
-        <v>78777</v>
+        <v>57821</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -24170,34 +24162,42 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>692957</v>
+        <v>691869</v>
       </c>
       <c r="R232" t="n">
-        <v>7105907</v>
+        <v>7106950</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -24244,12 +24244,12 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -24260,48 +24260,48 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>126869134</v>
+        <v>126862475</v>
       </c>
       <c r="B233" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Tällvattåsen, Ång</t>
+          <t>Tällvattsåsen, Ång</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691806</v>
+        <v>692904</v>
       </c>
       <c r="R233" t="n">
-        <v>7107033</v>
+        <v>7105978</v>
       </c>
       <c r="S233" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -24345,64 +24345,60 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Miriam Schenk</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
-        </is>
-      </c>
-      <c r="AY233" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Peter Andersson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>126862475</v>
+        <v>126869134</v>
       </c>
       <c r="B234" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Tällvattsåsen, Ång</t>
+          <t>Tällvattåsen, Ång</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>692904</v>
+        <v>691806</v>
       </c>
       <c r="R234" t="n">
-        <v>7105978</v>
+        <v>7107033</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -24446,15 +24442,19 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Miriam Schenk</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
-        </is>
-      </c>
-      <c r="AY234" t="inlineStr"/>
+          <t>Miriam Schenk, Lise Mortensen, Beke Regelin</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
